--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -29207,7 +29207,7 @@
         <v>104</v>
       </c>
       <c r="T2" s="7"/>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
@@ -29259,7 +29259,7 @@
       <c r="O3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t xml:space="preserve">Необязательный</t>
         </is>
@@ -29311,7 +29311,7 @@
       <c r="O4" t="s">
         <v>44</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ссылка на видео</t>
         </is>
@@ -29375,7 +29375,7 @@
       <c r="S5" t="s">
         <v>7963</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/fuqdd6mEaVF6EQ</t>
         </is>
@@ -29439,7 +29439,7 @@
       <c r="S6" t="s">
         <v>7963</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/R_2MXfnX3T3Ntw</t>
         </is>
@@ -29503,7 +29503,7 @@
       <c r="S7" t="s">
         <v>7963</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/Caf3UT24R06_hg</t>
         </is>
@@ -29567,7 +29567,7 @@
       <c r="S8" t="s">
         <v>7963</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/oc9RZ8Lx0w4XpQ</t>
         </is>
@@ -29631,7 +29631,7 @@
       <c r="S9" t="s">
         <v>7963</v>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/6s06BS76AivpdQ</t>
         </is>
@@ -29695,7 +29695,7 @@
       <c r="S10" t="s">
         <v>7963</v>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/uPc56ITyRGE3Gg</t>
         </is>
@@ -29759,7 +29759,7 @@
       <c r="S11" t="s">
         <v>7963</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/WoNmbD9ZWjkRwA</t>
         </is>
@@ -29823,7 +29823,7 @@
       <c r="S12" t="s">
         <v>7963</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/-Q5bdVzd3WIOvA</t>
         </is>
@@ -29887,7 +29887,7 @@
       <c r="S13" t="s">
         <v>7963</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/sTJxCT0V5irX4A</t>
         </is>
@@ -30234,7 +30234,7 @@
         <v>104</v>
       </c>
       <c r="AD2" s="7"/>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
@@ -30316,7 +30316,7 @@
       <c r="Y3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t xml:space="preserve">Необязательный</t>
         </is>
@@ -30398,7 +30398,7 @@
       <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ссылка на видео</t>
         </is>
@@ -37573,7 +37573,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD87" t="inlineStr">
+      <c r="AE87" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/_vmhz17RjUJqJQ</t>
         </is>
@@ -37705,7 +37705,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD88" t="inlineStr">
+      <c r="AE88" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/wMgQUTpqNCuwjg</t>
         </is>
@@ -37837,7 +37837,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD89" t="inlineStr">
+      <c r="AE89" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/o6IH59mUXAby0Q</t>
         </is>
@@ -37969,7 +37969,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD90" t="inlineStr">
+      <c r="AE90" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/Io87sSjfuT_16A</t>
         </is>
@@ -38101,7 +38101,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD91" t="inlineStr">
+      <c r="AE91" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/3w2RoL4oPjPrRA</t>
         </is>
@@ -38233,7 +38233,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD92" t="inlineStr">
+      <c r="AE92" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/QFgv2fVT-QGmDw</t>
         </is>
@@ -38365,7 +38365,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD93" t="inlineStr">
+      <c r="AE93" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/gxdIEZNTp_UERw</t>
         </is>
@@ -38497,7 +38497,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD94" t="inlineStr">
+      <c r="AE94" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/vJULBAjDHfnVBg</t>
         </is>
@@ -38629,7 +38629,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD95" t="inlineStr">
+      <c r="AE95" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/PGuf74v2ZUNyUA</t>
         </is>
@@ -38761,7 +38761,7 @@
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AD96" t="inlineStr">
+      <c r="AE96" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/S46l-rAlfcu3NQ</t>
         </is>
@@ -77891,7 +77891,7 @@
         <v>104</v>
       </c>
       <c r="V2" s="7"/>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
@@ -77946,7 +77946,7 @@
       <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t xml:space="preserve">Необязательный</t>
         </is>
@@ -78001,7 +78001,7 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ссылка на видео</t>
         </is>
@@ -78068,7 +78068,7 @@
       <c r="U5" t="s">
         <v>7963</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/fmCxUxBaEehBog</t>
         </is>

--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -29133,15 +29133,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="5" min="4" width="16"/>
-    <col customWidth="true" max="7" min="6" width="19"/>
-    <col customWidth="true" max="14" min="8" width="16"/>
-    <col customWidth="true" max="16" min="15" width="28.33"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -29194,20 +29185,20 @@
       <c r="O2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="T2" s="7"/>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="7"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
@@ -29259,7 +29250,7 @@
       <c r="O3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve">Необязательный</t>
         </is>
@@ -29311,11 +29302,6 @@
       <c r="O4" t="s">
         <v>44</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ссылка на видео</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -29363,19 +29349,19 @@
       <c r="O5" t="s">
         <v>97</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>8367</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>7961</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>7962</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>7963</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/fuqdd6mEaVF6EQ</t>
         </is>
@@ -29427,19 +29413,19 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>8374</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>7961</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>7962</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>7963</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/R_2MXfnX3T3Ntw</t>
         </is>
@@ -29491,19 +29477,19 @@
       <c r="O7" t="s">
         <v>97</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>8044</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>7961</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>7962</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>7963</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/Caf3UT24R06_hg</t>
         </is>
@@ -29555,19 +29541,19 @@
       <c r="O8" t="s">
         <v>97</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>8155</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>7961</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>7962</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>7963</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/oc9RZ8Lx0w4XpQ</t>
         </is>
@@ -29619,19 +29605,19 @@
       <c r="O9" t="s">
         <v>97</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>7972</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>7961</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>7962</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>7963</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/6s06BS76AivpdQ</t>
         </is>
@@ -29683,19 +29669,19 @@
       <c r="O10" t="s">
         <v>97</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>8398</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>7961</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>7962</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>7963</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/uPc56ITyRGE3Gg</t>
         </is>
@@ -29747,19 +29733,19 @@
       <c r="O11" t="s">
         <v>97</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>8404</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>7961</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>7962</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>7963</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/WoNmbD9ZWjkRwA</t>
         </is>
@@ -29811,19 +29797,19 @@
       <c r="O12" t="s">
         <v>97</v>
       </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>8229</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>7961</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>7962</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>7963</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/-Q5bdVzd3WIOvA</t>
         </is>
@@ -29875,19 +29861,19 @@
       <c r="O13" t="s">
         <v>97</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>7980</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>7961</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>7962</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>7963</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/sTJxCT0V5irX4A</t>
         </is>
@@ -30125,20 +30111,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="7" min="4" width="16"/>
-    <col customWidth="true" max="9" min="8" width="19"/>
-    <col customWidth="true" max="11" min="10" width="16"/>
-    <col customWidth="true" max="12" min="12" width="21"/>
-    <col customWidth="true" max="16" min="13" width="16"/>
-    <col customWidth="true" max="17" min="17" width="21"/>
-    <col customWidth="true" max="18" min="18" width="28.33"/>
-    <col customWidth="true" max="19" min="19" width="25"/>
-    <col customWidth="true" max="26" min="20" width="16"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -30221,20 +30193,20 @@
       <c r="Y2" s="7" t="s">
         <v>7896</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="AA2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AB2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AC2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AD2" s="7"/>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="7"/>
+      <c r="Z2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
@@ -30316,7 +30288,7 @@
       <c r="Y3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t xml:space="preserve">Необязательный</t>
         </is>
@@ -30398,11 +30370,6 @@
       <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ссылка на видео</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -30477,16 +30444,16 @@
       <c r="Y5" t="s">
         <v>7913</v>
       </c>
-      <c r="Z5" t="s">
+      <c r="AA5" t="s">
         <v>7960</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>7961</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>7962</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -30563,16 +30530,16 @@
       <c r="Y6" t="s">
         <v>7916</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AA6" t="s">
         <v>7972</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>7961</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>7962</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -30649,16 +30616,16 @@
       <c r="Y7" t="s">
         <v>7910</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AA7" t="s">
         <v>7980</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>7961</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>7962</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -30735,16 +30702,16 @@
       <c r="Y8" t="s">
         <v>7913</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AA8" t="s">
         <v>7987</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>7961</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AC8" t="s">
         <v>7962</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -30821,16 +30788,16 @@
       <c r="Y9" t="s">
         <v>7903</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="AA9" t="s">
         <v>7995</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>7961</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>7962</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -30907,16 +30874,16 @@
       <c r="Y10" t="s">
         <v>7913</v>
       </c>
-      <c r="Z10" t="s">
+      <c r="AA10" t="s">
         <v>8004</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>7961</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AC10" t="s">
         <v>7962</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AD10" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -30993,16 +30960,16 @@
       <c r="Y11" t="s">
         <v>7903</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AA11" t="s">
         <v>8004</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>7961</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AC11" t="s">
         <v>7962</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31079,16 +31046,16 @@
       <c r="Y12" t="s">
         <v>7903</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AA12" t="s">
         <v>7980</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>7961</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
         <v>7962</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AD12" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31165,16 +31132,16 @@
       <c r="Y13" t="s">
         <v>7913</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AA13" t="s">
         <v>7980</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>7961</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
         <v>7962</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31251,16 +31218,16 @@
       <c r="Y14" t="s">
         <v>7913</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AA14" t="s">
         <v>8004</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB14" t="s">
         <v>7961</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
         <v>7962</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AD14" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31337,16 +31304,16 @@
       <c r="Y15" t="s">
         <v>7913</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="AA15" t="s">
         <v>8034</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>7961</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
         <v>7962</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31423,16 +31390,16 @@
       <c r="Y16" t="s">
         <v>7913</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AA16" t="s">
         <v>8034</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>7961</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AC16" t="s">
         <v>7962</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AD16" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31509,16 +31476,16 @@
       <c r="Y17" t="s">
         <v>7913</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AA17" t="s">
         <v>8044</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>7961</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AC17" t="s">
         <v>7962</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31598,16 +31565,16 @@
       <c r="Y18" t="s">
         <v>7913</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AA18" t="s">
         <v>7995</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>7961</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AC18" t="s">
         <v>7962</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AD18" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31684,16 +31651,16 @@
       <c r="Y19" t="s">
         <v>7916</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AA19" t="s">
         <v>8054</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB19" t="s">
         <v>7961</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AC19" t="s">
         <v>7962</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AD19" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31770,16 +31737,16 @@
       <c r="Y20" t="s">
         <v>7913</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AA20" t="s">
         <v>8004</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>7961</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AC20" t="s">
         <v>7962</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AD20" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31856,16 +31823,16 @@
       <c r="Y21" t="s">
         <v>7916</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
         <v>8065</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" t="s">
         <v>7961</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AC21" t="s">
         <v>7962</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AD21" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -31942,16 +31909,16 @@
       <c r="Y22" t="s">
         <v>7903</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AA22" t="s">
         <v>7972</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AB22" t="s">
         <v>7961</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AC22" t="s">
         <v>7962</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="AD22" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32028,16 +31995,16 @@
       <c r="Y23" t="s">
         <v>7913</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>8004</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>7961</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AC23" t="s">
         <v>7962</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AD23" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32114,16 +32081,16 @@
       <c r="Y24" t="s">
         <v>7913</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AA24" t="s">
         <v>8044</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB24" t="s">
         <v>7961</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AC24" t="s">
         <v>7962</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32200,16 +32167,16 @@
       <c r="Y25" t="s">
         <v>7913</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AA25" t="s">
         <v>8065</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>7961</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AC25" t="s">
         <v>7962</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AD25" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32286,16 +32253,16 @@
       <c r="Y26" t="s">
         <v>7913</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AA26" t="s">
         <v>8089</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>7961</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AC26" t="s">
         <v>7962</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AD26" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32372,16 +32339,16 @@
       <c r="Y27" t="s">
         <v>7913</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AA27" t="s">
         <v>8004</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>7961</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AC27" t="s">
         <v>7962</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AD27" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32458,16 +32425,16 @@
       <c r="Y28" t="s">
         <v>7913</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AA28" t="s">
         <v>8004</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>7961</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>7962</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AD28" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32544,16 +32511,16 @@
       <c r="Y29" t="s">
         <v>7912</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AA29" t="s">
         <v>7960</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>7961</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
         <v>7962</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AD29" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32630,16 +32597,16 @@
       <c r="Y30" t="s">
         <v>7913</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>8089</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>7961</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
         <v>7962</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AD30" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32716,16 +32683,16 @@
       <c r="Y31" t="s">
         <v>7913</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AA31" t="s">
         <v>8044</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AB31" t="s">
         <v>7961</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AC31" t="s">
         <v>7962</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AD31" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32802,16 +32769,16 @@
       <c r="Y32" t="s">
         <v>7910</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AA32" t="s">
         <v>8054</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>7961</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>7962</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AD32" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32888,16 +32855,16 @@
       <c r="Y33" t="s">
         <v>7913</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AA33" t="s">
         <v>8044</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AB33" t="s">
         <v>7961</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AC33" t="s">
         <v>7962</v>
       </c>
-      <c r="AC33" t="s">
+      <c r="AD33" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -32974,16 +32941,16 @@
       <c r="Y34" t="s">
         <v>7916</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AA34" t="s">
         <v>7972</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AB34" t="s">
         <v>7961</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AC34" t="s">
         <v>7962</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AD34" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33060,16 +33027,16 @@
       <c r="Y35" t="s">
         <v>7913</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AA35" t="s">
         <v>8130</v>
       </c>
-      <c r="AA35" t="s">
+      <c r="AB35" t="s">
         <v>7961</v>
       </c>
-      <c r="AB35" t="s">
+      <c r="AC35" t="s">
         <v>7962</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="AD35" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33149,16 +33116,16 @@
       <c r="Y36" t="s">
         <v>7913</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AA36" t="s">
         <v>7980</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AB36" t="s">
         <v>7961</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AC36" t="s">
         <v>7962</v>
       </c>
-      <c r="AC36" t="s">
+      <c r="AD36" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33232,16 +33199,16 @@
       <c r="Y37" t="s">
         <v>7913</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AA37" t="s">
         <v>7972</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AB37" t="s">
         <v>7961</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AC37" t="s">
         <v>7962</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AD37" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33318,16 +33285,16 @@
       <c r="Y38" t="s">
         <v>7910</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AA38" t="s">
         <v>8145</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>7961</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AC38" t="s">
         <v>7962</v>
       </c>
-      <c r="AC38" t="s">
+      <c r="AD38" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33404,16 +33371,16 @@
       <c r="Y39" t="s">
         <v>7913</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AA39" t="s">
         <v>8044</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AB39" t="s">
         <v>7961</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AC39" t="s">
         <v>7962</v>
       </c>
-      <c r="AC39" t="s">
+      <c r="AD39" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33490,16 +33457,16 @@
       <c r="Y40" t="s">
         <v>7913</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AA40" t="s">
         <v>8155</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AB40" t="s">
         <v>7961</v>
       </c>
-      <c r="AB40" t="s">
+      <c r="AC40" t="s">
         <v>7962</v>
       </c>
-      <c r="AC40" t="s">
+      <c r="AD40" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33576,16 +33543,16 @@
       <c r="Y41" t="s">
         <v>7913</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="AA41" t="s">
         <v>8004</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AB41" t="s">
         <v>7961</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AC41" t="s">
         <v>7962</v>
       </c>
-      <c r="AC41" t="s">
+      <c r="AD41" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33662,16 +33629,16 @@
       <c r="Y42" t="s">
         <v>7913</v>
       </c>
-      <c r="Z42" t="s">
+      <c r="AA42" t="s">
         <v>8004</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="AB42" t="s">
         <v>7961</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AC42" t="s">
         <v>7962</v>
       </c>
-      <c r="AC42" t="s">
+      <c r="AD42" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33748,16 +33715,16 @@
       <c r="Y43" t="s">
         <v>7913</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="AA43" t="s">
         <v>8130</v>
       </c>
-      <c r="AA43" t="s">
+      <c r="AB43" t="s">
         <v>7961</v>
       </c>
-      <c r="AB43" t="s">
+      <c r="AC43" t="s">
         <v>7962</v>
       </c>
-      <c r="AC43" t="s">
+      <c r="AD43" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33834,16 +33801,16 @@
       <c r="Y44" t="s">
         <v>7913</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="AA44" t="s">
         <v>8044</v>
       </c>
-      <c r="AA44" t="s">
+      <c r="AB44" t="s">
         <v>7961</v>
       </c>
-      <c r="AB44" t="s">
+      <c r="AC44" t="s">
         <v>7962</v>
       </c>
-      <c r="AC44" t="s">
+      <c r="AD44" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -33920,16 +33887,16 @@
       <c r="Y45" t="s">
         <v>7913</v>
       </c>
-      <c r="Z45" t="s">
+      <c r="AA45" t="s">
         <v>7960</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="AB45" t="s">
         <v>7961</v>
       </c>
-      <c r="AB45" t="s">
+      <c r="AC45" t="s">
         <v>7962</v>
       </c>
-      <c r="AC45" t="s">
+      <c r="AD45" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34006,16 +33973,16 @@
       <c r="Y46" t="s">
         <v>7913</v>
       </c>
-      <c r="Z46" t="s">
+      <c r="AA46" t="s">
         <v>7972</v>
       </c>
-      <c r="AA46" t="s">
+      <c r="AB46" t="s">
         <v>7961</v>
       </c>
-      <c r="AB46" t="s">
+      <c r="AC46" t="s">
         <v>7962</v>
       </c>
-      <c r="AC46" t="s">
+      <c r="AD46" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34092,16 +34059,16 @@
       <c r="Y47" t="s">
         <v>7913</v>
       </c>
-      <c r="Z47" t="s">
+      <c r="AA47" t="s">
         <v>7980</v>
       </c>
-      <c r="AA47" t="s">
+      <c r="AB47" t="s">
         <v>7961</v>
       </c>
-      <c r="AB47" t="s">
+      <c r="AC47" t="s">
         <v>7962</v>
       </c>
-      <c r="AC47" t="s">
+      <c r="AD47" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34178,16 +34145,16 @@
       <c r="Y48" t="s">
         <v>7912</v>
       </c>
-      <c r="Z48" t="s">
+      <c r="AA48" t="s">
         <v>7987</v>
       </c>
-      <c r="AA48" t="s">
+      <c r="AB48" t="s">
         <v>7961</v>
       </c>
-      <c r="AB48" t="s">
+      <c r="AC48" t="s">
         <v>7962</v>
       </c>
-      <c r="AC48" t="s">
+      <c r="AD48" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34264,16 +34231,16 @@
       <c r="Y49" t="s">
         <v>7913</v>
       </c>
-      <c r="Z49" t="s">
+      <c r="AA49" t="s">
         <v>8004</v>
       </c>
-      <c r="AA49" t="s">
+      <c r="AB49" t="s">
         <v>7961</v>
       </c>
-      <c r="AB49" t="s">
+      <c r="AC49" t="s">
         <v>7962</v>
       </c>
-      <c r="AC49" t="s">
+      <c r="AD49" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34347,16 +34314,16 @@
       <c r="Y50" t="s">
         <v>7913</v>
       </c>
-      <c r="Z50" t="s">
+      <c r="AA50" t="s">
         <v>8065</v>
       </c>
-      <c r="AA50" t="s">
+      <c r="AB50" t="s">
         <v>7961</v>
       </c>
-      <c r="AB50" t="s">
+      <c r="AC50" t="s">
         <v>7962</v>
       </c>
-      <c r="AC50" t="s">
+      <c r="AD50" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34433,16 +34400,16 @@
       <c r="Y51" t="s">
         <v>7913</v>
       </c>
-      <c r="Z51" t="s">
+      <c r="AA51" t="s">
         <v>7972</v>
       </c>
-      <c r="AA51" t="s">
+      <c r="AB51" t="s">
         <v>7961</v>
       </c>
-      <c r="AB51" t="s">
+      <c r="AC51" t="s">
         <v>7962</v>
       </c>
-      <c r="AC51" t="s">
+      <c r="AD51" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34519,16 +34486,16 @@
       <c r="Y52" t="s">
         <v>7913</v>
       </c>
-      <c r="Z52" t="s">
+      <c r="AA52" t="s">
         <v>7980</v>
       </c>
-      <c r="AA52" t="s">
+      <c r="AB52" t="s">
         <v>7961</v>
       </c>
-      <c r="AB52" t="s">
+      <c r="AC52" t="s">
         <v>7962</v>
       </c>
-      <c r="AC52" t="s">
+      <c r="AD52" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34605,16 +34572,16 @@
       <c r="Y53" t="s">
         <v>7903</v>
       </c>
-      <c r="Z53" t="s">
+      <c r="AA53" t="s">
         <v>8004</v>
       </c>
-      <c r="AA53" t="s">
+      <c r="AB53" t="s">
         <v>7961</v>
       </c>
-      <c r="AB53" t="s">
+      <c r="AC53" t="s">
         <v>7962</v>
       </c>
-      <c r="AC53" t="s">
+      <c r="AD53" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34691,16 +34658,16 @@
       <c r="Y54" t="s">
         <v>7913</v>
       </c>
-      <c r="Z54" t="s">
+      <c r="AA54" t="s">
         <v>8155</v>
       </c>
-      <c r="AA54" t="s">
+      <c r="AB54" t="s">
         <v>7961</v>
       </c>
-      <c r="AB54" t="s">
+      <c r="AC54" t="s">
         <v>7962</v>
       </c>
-      <c r="AC54" t="s">
+      <c r="AD54" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34777,16 +34744,16 @@
       <c r="Y55" t="s">
         <v>7913</v>
       </c>
-      <c r="Z55" t="s">
+      <c r="AA55" t="s">
         <v>8054</v>
       </c>
-      <c r="AA55" t="s">
+      <c r="AB55" t="s">
         <v>7961</v>
       </c>
-      <c r="AB55" t="s">
+      <c r="AC55" t="s">
         <v>7962</v>
       </c>
-      <c r="AC55" t="s">
+      <c r="AD55" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34863,16 +34830,16 @@
       <c r="Y56" t="s">
         <v>7913</v>
       </c>
-      <c r="Z56" t="s">
+      <c r="AA56" t="s">
         <v>8044</v>
       </c>
-      <c r="AA56" t="s">
+      <c r="AB56" t="s">
         <v>7961</v>
       </c>
-      <c r="AB56" t="s">
+      <c r="AC56" t="s">
         <v>7962</v>
       </c>
-      <c r="AC56" t="s">
+      <c r="AD56" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -34949,16 +34916,16 @@
       <c r="Y57" t="s">
         <v>7903</v>
       </c>
-      <c r="Z57" t="s">
+      <c r="AA57" t="s">
         <v>8229</v>
       </c>
-      <c r="AA57" t="s">
+      <c r="AB57" t="s">
         <v>7961</v>
       </c>
-      <c r="AB57" t="s">
+      <c r="AC57" t="s">
         <v>7962</v>
       </c>
-      <c r="AC57" t="s">
+      <c r="AD57" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35035,16 +35002,16 @@
       <c r="Y58" t="s">
         <v>7913</v>
       </c>
-      <c r="Z58" t="s">
+      <c r="AA58" t="s">
         <v>7980</v>
       </c>
-      <c r="AA58" t="s">
+      <c r="AB58" t="s">
         <v>7961</v>
       </c>
-      <c r="AB58" t="s">
+      <c r="AC58" t="s">
         <v>7962</v>
       </c>
-      <c r="AC58" t="s">
+      <c r="AD58" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35121,16 +35088,16 @@
       <c r="Y59" t="s">
         <v>7912</v>
       </c>
-      <c r="Z59" t="s">
+      <c r="AA59" t="s">
         <v>8054</v>
       </c>
-      <c r="AA59" t="s">
+      <c r="AB59" t="s">
         <v>7961</v>
       </c>
-      <c r="AB59" t="s">
+      <c r="AC59" t="s">
         <v>7962</v>
       </c>
-      <c r="AC59" t="s">
+      <c r="AD59" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35207,16 +35174,16 @@
       <c r="Y60" t="s">
         <v>7913</v>
       </c>
-      <c r="Z60" t="s">
+      <c r="AA60" t="s">
         <v>8242</v>
       </c>
-      <c r="AA60" t="s">
+      <c r="AB60" t="s">
         <v>7961</v>
       </c>
-      <c r="AB60" t="s">
+      <c r="AC60" t="s">
         <v>7962</v>
       </c>
-      <c r="AC60" t="s">
+      <c r="AD60" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35290,16 +35257,16 @@
       <c r="Y61" t="s">
         <v>7913</v>
       </c>
-      <c r="Z61" t="s">
+      <c r="AA61" t="s">
         <v>7987</v>
       </c>
-      <c r="AA61" t="s">
+      <c r="AB61" t="s">
         <v>7961</v>
       </c>
-      <c r="AB61" t="s">
+      <c r="AC61" t="s">
         <v>7962</v>
       </c>
-      <c r="AC61" t="s">
+      <c r="AD61" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35376,16 +35343,16 @@
       <c r="Y62" t="s">
         <v>7912</v>
       </c>
-      <c r="Z62" t="s">
+      <c r="AA62" t="s">
         <v>8251</v>
       </c>
-      <c r="AA62" t="s">
+      <c r="AB62" t="s">
         <v>7961</v>
       </c>
-      <c r="AB62" t="s">
+      <c r="AC62" t="s">
         <v>7962</v>
       </c>
-      <c r="AC62" t="s">
+      <c r="AD62" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35459,16 +35426,16 @@
       <c r="Y63" t="s">
         <v>7905</v>
       </c>
-      <c r="Z63" t="s">
+      <c r="AA63" t="s">
         <v>8044</v>
       </c>
-      <c r="AA63" t="s">
+      <c r="AB63" t="s">
         <v>7961</v>
       </c>
-      <c r="AB63" t="s">
+      <c r="AC63" t="s">
         <v>7962</v>
       </c>
-      <c r="AC63" t="s">
+      <c r="AD63" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35545,16 +35512,16 @@
       <c r="Y64" t="s">
         <v>7913</v>
       </c>
-      <c r="Z64" t="s">
+      <c r="AA64" t="s">
         <v>8044</v>
       </c>
-      <c r="AA64" t="s">
+      <c r="AB64" t="s">
         <v>7961</v>
       </c>
-      <c r="AB64" t="s">
+      <c r="AC64" t="s">
         <v>7962</v>
       </c>
-      <c r="AC64" t="s">
+      <c r="AD64" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35631,16 +35598,16 @@
       <c r="Y65" t="s">
         <v>7913</v>
       </c>
-      <c r="Z65" t="s">
+      <c r="AA65" t="s">
         <v>7960</v>
       </c>
-      <c r="AA65" t="s">
+      <c r="AB65" t="s">
         <v>7961</v>
       </c>
-      <c r="AB65" t="s">
+      <c r="AC65" t="s">
         <v>7962</v>
       </c>
-      <c r="AC65" t="s">
+      <c r="AD65" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35717,16 +35684,16 @@
       <c r="Y66" t="s">
         <v>7910</v>
       </c>
-      <c r="Z66" t="s">
+      <c r="AA66" t="s">
         <v>7972</v>
       </c>
-      <c r="AA66" t="s">
+      <c r="AB66" t="s">
         <v>7961</v>
       </c>
-      <c r="AB66" t="s">
+      <c r="AC66" t="s">
         <v>7962</v>
       </c>
-      <c r="AC66" t="s">
+      <c r="AD66" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35803,16 +35770,16 @@
       <c r="Y67" t="s">
         <v>7913</v>
       </c>
-      <c r="Z67" t="s">
+      <c r="AA67" t="s">
         <v>8130</v>
       </c>
-      <c r="AA67" t="s">
+      <c r="AB67" t="s">
         <v>7961</v>
       </c>
-      <c r="AB67" t="s">
+      <c r="AC67" t="s">
         <v>7962</v>
       </c>
-      <c r="AC67" t="s">
+      <c r="AD67" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35889,16 +35856,16 @@
       <c r="Y68" t="s">
         <v>7903</v>
       </c>
-      <c r="Z68" t="s">
+      <c r="AA68" t="s">
         <v>8004</v>
       </c>
-      <c r="AA68" t="s">
+      <c r="AB68" t="s">
         <v>7961</v>
       </c>
-      <c r="AB68" t="s">
+      <c r="AC68" t="s">
         <v>7962</v>
       </c>
-      <c r="AC68" t="s">
+      <c r="AD68" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -35975,16 +35942,16 @@
       <c r="Y69" t="s">
         <v>7913</v>
       </c>
-      <c r="Z69" t="s">
+      <c r="AA69" t="s">
         <v>7980</v>
       </c>
-      <c r="AA69" t="s">
+      <c r="AB69" t="s">
         <v>7961</v>
       </c>
-      <c r="AB69" t="s">
+      <c r="AC69" t="s">
         <v>7962</v>
       </c>
-      <c r="AC69" t="s">
+      <c r="AD69" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36061,16 +36028,16 @@
       <c r="Y70" t="s">
         <v>7913</v>
       </c>
-      <c r="Z70" t="s">
+      <c r="AA70" t="s">
         <v>8004</v>
       </c>
-      <c r="AA70" t="s">
+      <c r="AB70" t="s">
         <v>7961</v>
       </c>
-      <c r="AB70" t="s">
+      <c r="AC70" t="s">
         <v>7962</v>
       </c>
-      <c r="AC70" t="s">
+      <c r="AD70" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36147,16 +36114,16 @@
       <c r="Y71" t="s">
         <v>7913</v>
       </c>
-      <c r="Z71" t="s">
+      <c r="AA71" t="s">
         <v>8293</v>
       </c>
-      <c r="AA71" t="s">
+      <c r="AB71" t="s">
         <v>7961</v>
       </c>
-      <c r="AB71" t="s">
+      <c r="AC71" t="s">
         <v>7962</v>
       </c>
-      <c r="AC71" t="s">
+      <c r="AD71" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36233,16 +36200,16 @@
       <c r="Y72" t="s">
         <v>7913</v>
       </c>
-      <c r="Z72" t="s">
+      <c r="AA72" t="s">
         <v>8229</v>
       </c>
-      <c r="AA72" t="s">
+      <c r="AB72" t="s">
         <v>7961</v>
       </c>
-      <c r="AB72" t="s">
+      <c r="AC72" t="s">
         <v>7962</v>
       </c>
-      <c r="AC72" t="s">
+      <c r="AD72" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36319,16 +36286,16 @@
       <c r="Y73" t="s">
         <v>7913</v>
       </c>
-      <c r="Z73" t="s">
+      <c r="AA73" t="s">
         <v>7980</v>
       </c>
-      <c r="AA73" t="s">
+      <c r="AB73" t="s">
         <v>7961</v>
       </c>
-      <c r="AB73" t="s">
+      <c r="AC73" t="s">
         <v>7962</v>
       </c>
-      <c r="AC73" t="s">
+      <c r="AD73" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36405,16 +36372,16 @@
       <c r="Y74" t="s">
         <v>7913</v>
       </c>
-      <c r="Z74" t="s">
+      <c r="AA74" t="s">
         <v>7960</v>
       </c>
-      <c r="AA74" t="s">
+      <c r="AB74" t="s">
         <v>7961</v>
       </c>
-      <c r="AB74" t="s">
+      <c r="AC74" t="s">
         <v>7962</v>
       </c>
-      <c r="AC74" t="s">
+      <c r="AD74" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36491,16 +36458,16 @@
       <c r="Y75" t="s">
         <v>7912</v>
       </c>
-      <c r="Z75" t="s">
+      <c r="AA75" t="s">
         <v>8044</v>
       </c>
-      <c r="AA75" t="s">
+      <c r="AB75" t="s">
         <v>7961</v>
       </c>
-      <c r="AB75" t="s">
+      <c r="AC75" t="s">
         <v>7962</v>
       </c>
-      <c r="AC75" t="s">
+      <c r="AD75" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36577,16 +36544,16 @@
       <c r="Y76" t="s">
         <v>7913</v>
       </c>
-      <c r="Z76" t="s">
+      <c r="AA76" t="s">
         <v>8229</v>
       </c>
-      <c r="AA76" t="s">
+      <c r="AB76" t="s">
         <v>7961</v>
       </c>
-      <c r="AB76" t="s">
+      <c r="AC76" t="s">
         <v>7962</v>
       </c>
-      <c r="AC76" t="s">
+      <c r="AD76" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36663,16 +36630,16 @@
       <c r="Y77" t="s">
         <v>7913</v>
       </c>
-      <c r="Z77" t="s">
+      <c r="AA77" t="s">
         <v>8044</v>
       </c>
-      <c r="AA77" t="s">
+      <c r="AB77" t="s">
         <v>7961</v>
       </c>
-      <c r="AB77" t="s">
+      <c r="AC77" t="s">
         <v>7962</v>
       </c>
-      <c r="AC77" t="s">
+      <c r="AD77" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36749,16 +36716,16 @@
       <c r="Y78" t="s">
         <v>7912</v>
       </c>
-      <c r="Z78" t="s">
+      <c r="AA78" t="s">
         <v>7987</v>
       </c>
-      <c r="AA78" t="s">
+      <c r="AB78" t="s">
         <v>7961</v>
       </c>
-      <c r="AB78" t="s">
+      <c r="AC78" t="s">
         <v>7962</v>
       </c>
-      <c r="AC78" t="s">
+      <c r="AD78" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36835,16 +36802,16 @@
       <c r="Y79" t="s">
         <v>7903</v>
       </c>
-      <c r="Z79" t="s">
+      <c r="AA79" t="s">
         <v>8044</v>
       </c>
-      <c r="AA79" t="s">
+      <c r="AB79" t="s">
         <v>7961</v>
       </c>
-      <c r="AB79" t="s">
+      <c r="AC79" t="s">
         <v>7962</v>
       </c>
-      <c r="AC79" t="s">
+      <c r="AD79" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -36921,16 +36888,16 @@
       <c r="Y80" t="s">
         <v>7910</v>
       </c>
-      <c r="Z80" t="s">
+      <c r="AA80" t="s">
         <v>8004</v>
       </c>
-      <c r="AA80" t="s">
+      <c r="AB80" t="s">
         <v>7961</v>
       </c>
-      <c r="AB80" t="s">
+      <c r="AC80" t="s">
         <v>7962</v>
       </c>
-      <c r="AC80" t="s">
+      <c r="AD80" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -37007,16 +36974,16 @@
       <c r="Y81" t="s">
         <v>7913</v>
       </c>
-      <c r="Z81" t="s">
+      <c r="AA81" t="s">
         <v>8004</v>
       </c>
-      <c r="AA81" t="s">
+      <c r="AB81" t="s">
         <v>7961</v>
       </c>
-      <c r="AB81" t="s">
+      <c r="AC81" t="s">
         <v>7962</v>
       </c>
-      <c r="AC81" t="s">
+      <c r="AD81" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -37093,16 +37060,16 @@
       <c r="Y82" t="s">
         <v>7913</v>
       </c>
-      <c r="Z82" t="s">
+      <c r="AA82" t="s">
         <v>8341</v>
       </c>
-      <c r="AA82" t="s">
+      <c r="AB82" t="s">
         <v>7961</v>
       </c>
-      <c r="AB82" t="s">
+      <c r="AC82" t="s">
         <v>7962</v>
       </c>
-      <c r="AC82" t="s">
+      <c r="AD82" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -37179,16 +37146,16 @@
       <c r="Y83" t="s">
         <v>7913</v>
       </c>
-      <c r="Z83" t="s">
+      <c r="AA83" t="s">
         <v>8054</v>
       </c>
-      <c r="AA83" t="s">
+      <c r="AB83" t="s">
         <v>7961</v>
       </c>
-      <c r="AB83" t="s">
+      <c r="AC83" t="s">
         <v>7962</v>
       </c>
-      <c r="AC83" t="s">
+      <c r="AD83" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -37265,16 +37232,16 @@
       <c r="Y84" t="s">
         <v>7913</v>
       </c>
-      <c r="Z84" t="s">
+      <c r="AA84" t="s">
         <v>8065</v>
       </c>
-      <c r="AA84" t="s">
+      <c r="AB84" t="s">
         <v>7961</v>
       </c>
-      <c r="AB84" t="s">
+      <c r="AC84" t="s">
         <v>7962</v>
       </c>
-      <c r="AC84" t="s">
+      <c r="AD84" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -37351,16 +37318,16 @@
       <c r="Y85" t="s">
         <v>7913</v>
       </c>
-      <c r="Z85" t="s">
+      <c r="AA85" t="s">
         <v>7972</v>
       </c>
-      <c r="AA85" t="s">
+      <c r="AB85" t="s">
         <v>7961</v>
       </c>
-      <c r="AB85" t="s">
+      <c r="AC85" t="s">
         <v>7962</v>
       </c>
-      <c r="AC85" t="s">
+      <c r="AD85" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -37434,16 +37401,16 @@
       <c r="Y86" t="s">
         <v>7913</v>
       </c>
-      <c r="Z86" t="s">
+      <c r="AA86" t="s">
         <v>8229</v>
       </c>
-      <c r="AA86" t="s">
+      <c r="AB86" t="s">
         <v>7961</v>
       </c>
-      <c r="AB86" t="s">
+      <c r="AC86" t="s">
         <v>7962</v>
       </c>
-      <c r="AC86" t="s">
+      <c r="AD86" t="s">
         <v>7963</v>
       </c>
     </row>
@@ -37563,17 +37530,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
+      <c r="AD87" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/_vmhz17RjUJqJQ</t>
         </is>
@@ -37695,17 +37662,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
+      <c r="AD88" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/wMgQUTpqNCuwjg</t>
         </is>
@@ -37827,17 +37794,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
+      <c r="AD89" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/o6IH59mUXAby0Q</t>
         </is>
@@ -37959,17 +37926,17 @@
           <t xml:space="preserve">Силикон</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
+      <c r="AD90" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/Io87sSjfuT_16A</t>
         </is>
@@ -38091,17 +38058,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
+      <c r="AD91" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/3w2RoL4oPjPrRA</t>
         </is>
@@ -38223,17 +38190,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
+      <c r="AD92" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/QFgv2fVT-QGmDw</t>
         </is>
@@ -38355,17 +38322,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
+      <c r="AD93" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/gxdIEZNTp_UERw</t>
         </is>
@@ -38487,17 +38454,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
+      <c r="AD94" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/vJULBAjDHfnVBg</t>
         </is>
@@ -38619,17 +38586,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
+      <c r="AD95" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/PGuf74v2ZUNyUA</t>
         </is>
@@ -38751,17 +38718,17 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
+      <c r="AD96" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
       </c>
-      <c r="AE96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/S46l-rAlfcu3NQ</t>
         </is>
@@ -77810,16 +77777,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" width="28.33"/>
-    <col customWidth="true" max="2" min="2" width="17"/>
-    <col customWidth="true" max="3" min="3" width="25"/>
-    <col customWidth="true" max="7" min="4" width="16"/>
-    <col customWidth="true" max="8" min="8" width="19"/>
-    <col customWidth="true" max="9" min="9" width="16"/>
-    <col customWidth="true" max="10" min="10" width="19"/>
-    <col customWidth="true" max="17" min="11" width="16"/>
-  </cols>
   <sheetData>
     <row r="1" ht="50" customHeight="true">
       <c r="A1" s="4" t="s">
@@ -77875,23 +77832,23 @@
       <c r="P2" s="7" t="s">
         <v>7943</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>7950</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="V2" s="7"/>
-      <c r="W2" t="inlineStr">
+      <c r="W2" s="7"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
@@ -77946,7 +77903,7 @@
       <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">Необязательный</t>
         </is>
@@ -78001,11 +77958,6 @@
       <c r="P4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ссылка на видео</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -78053,22 +78005,22 @@
       <c r="O5" t="s">
         <v>87</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>7962</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>8130</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>7961</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>8420</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>7963</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/fmCxUxBaEehBog</t>
         </is>

--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -29185,24 +29185,29 @@
       <c r="O2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
       <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -29255,6 +29260,11 @@
           <t xml:space="preserve">Необязательный</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -29349,16 +29359,16 @@
       <c r="O5" t="s">
         <v>97</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>8367</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>7961</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>7962</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>7963</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -29366,6 +29376,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/fuqdd6mEaVF6EQ</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -29413,16 +29428,16 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>8374</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>7961</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>7962</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>7963</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -29430,6 +29445,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/R_2MXfnX3T3Ntw</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -29477,16 +29497,16 @@
       <c r="O7" t="s">
         <v>97</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>8044</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>7961</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>7962</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>7963</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -29494,6 +29514,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/Caf3UT24R06_hg</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -29541,16 +29566,16 @@
       <c r="O8" t="s">
         <v>97</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>8155</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>7961</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>7962</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>7963</v>
       </c>
       <c r="P8" t="inlineStr">
@@ -29558,6 +29583,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/oc9RZ8Lx0w4XpQ</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -29605,16 +29635,16 @@
       <c r="O9" t="s">
         <v>97</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>7972</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>7961</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>7962</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>7963</v>
       </c>
       <c r="P9" t="inlineStr">
@@ -29622,6 +29652,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/6s06BS76AivpdQ</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -29669,16 +29704,16 @@
       <c r="O10" t="s">
         <v>97</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>8398</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>7961</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>7962</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>7963</v>
       </c>
       <c r="P10" t="inlineStr">
@@ -29686,6 +29721,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/uPc56ITyRGE3Gg</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -29733,16 +29773,16 @@
       <c r="O11" t="s">
         <v>97</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>8404</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>7961</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>7962</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>7963</v>
       </c>
       <c r="P11" t="inlineStr">
@@ -29750,6 +29790,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/WoNmbD9ZWjkRwA</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -29797,16 +29842,16 @@
       <c r="O12" t="s">
         <v>97</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>8229</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>7961</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>7962</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>7963</v>
       </c>
       <c r="P12" t="inlineStr">
@@ -29814,6 +29859,11 @@
           <t xml:space="preserve">https://disk.yandex.ru/i/-Q5bdVzd3WIOvA</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -29861,21 +29911,26 @@
       <c r="O13" t="s">
         <v>97</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>7980</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>7961</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>7962</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
         <v>7963</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/sTJxCT0V5irX4A</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -30193,24 +30248,29 @@
       <c r="Y2" s="7" t="s">
         <v>7896</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AB2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="AB2" s="7" t="s">
+      <c r="AC2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="AC2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="AD2" s="7" t="s">
+      <c r="AE2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
       <c r="Z2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -30293,6 +30353,11 @@
           <t xml:space="preserve">Необязательный</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -30444,17 +30509,22 @@
       <c r="Y5" t="s">
         <v>7913</v>
       </c>
-      <c r="AA5" t="s">
+      <c r="AB5" t="s">
         <v>7960</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>7961</v>
       </c>
-      <c r="AC5" t="s">
+      <c r="AD5" t="s">
         <v>7962</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AE5" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -30530,17 +30600,22 @@
       <c r="Y6" t="s">
         <v>7916</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AB6" t="s">
         <v>7972</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>7961</v>
       </c>
-      <c r="AC6" t="s">
+      <c r="AD6" t="s">
         <v>7962</v>
       </c>
-      <c r="AD6" t="s">
+      <c r="AE6" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -30616,17 +30691,22 @@
       <c r="Y7" t="s">
         <v>7910</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AB7" t="s">
         <v>7980</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>7961</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>7962</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -30702,17 +30782,22 @@
       <c r="Y8" t="s">
         <v>7913</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>7987</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AC8" t="s">
         <v>7961</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AD8" t="s">
         <v>7962</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -30788,17 +30873,22 @@
       <c r="Y9" t="s">
         <v>7903</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>7995</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>7961</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AD9" t="s">
         <v>7962</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -30874,17 +30964,22 @@
       <c r="Y10" t="s">
         <v>7913</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="AB10" t="s">
         <v>8004</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AC10" t="s">
         <v>7961</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AD10" t="s">
         <v>7962</v>
       </c>
-      <c r="AD10" t="s">
+      <c r="AE10" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -30960,17 +31055,22 @@
       <c r="Y11" t="s">
         <v>7903</v>
       </c>
-      <c r="AA11" t="s">
+      <c r="AB11" t="s">
         <v>8004</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AC11" t="s">
         <v>7961</v>
       </c>
-      <c r="AC11" t="s">
+      <c r="AD11" t="s">
         <v>7962</v>
       </c>
-      <c r="AD11" t="s">
+      <c r="AE11" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -31046,17 +31146,22 @@
       <c r="Y12" t="s">
         <v>7903</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AB12" t="s">
         <v>7980</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
         <v>7961</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AD12" t="s">
         <v>7962</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AE12" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -31132,17 +31237,22 @@
       <c r="Y13" t="s">
         <v>7913</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AB13" t="s">
         <v>7980</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
         <v>7961</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AD13" t="s">
         <v>7962</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AE13" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -31218,17 +31328,22 @@
       <c r="Y14" t="s">
         <v>7913</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AB14" t="s">
         <v>8004</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
         <v>7961</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AD14" t="s">
         <v>7962</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AE14" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -31304,17 +31419,22 @@
       <c r="Y15" t="s">
         <v>7913</v>
       </c>
-      <c r="AA15" t="s">
+      <c r="AB15" t="s">
         <v>8034</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
         <v>7961</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
         <v>7962</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AE15" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -31390,17 +31510,22 @@
       <c r="Y16" t="s">
         <v>7913</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AB16" t="s">
         <v>8034</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AC16" t="s">
         <v>7961</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AD16" t="s">
         <v>7962</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AE16" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -31476,17 +31601,22 @@
       <c r="Y17" t="s">
         <v>7913</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AB17" t="s">
         <v>8044</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AC17" t="s">
         <v>7961</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AD17" t="s">
         <v>7962</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AE17" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -31565,17 +31695,22 @@
       <c r="Y18" t="s">
         <v>7913</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AB18" t="s">
         <v>7995</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AC18" t="s">
         <v>7961</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AD18" t="s">
         <v>7962</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AE18" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -31651,17 +31786,22 @@
       <c r="Y19" t="s">
         <v>7916</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AB19" t="s">
         <v>8054</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AC19" t="s">
         <v>7961</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AD19" t="s">
         <v>7962</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AE19" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -31737,17 +31877,22 @@
       <c r="Y20" t="s">
         <v>7913</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AB20" t="s">
         <v>8004</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AC20" t="s">
         <v>7961</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AD20" t="s">
         <v>7962</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AE20" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -31823,17 +31968,22 @@
       <c r="Y21" t="s">
         <v>7916</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AB21" t="s">
         <v>8065</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AC21" t="s">
         <v>7961</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AD21" t="s">
         <v>7962</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -31909,17 +32059,22 @@
       <c r="Y22" t="s">
         <v>7903</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AB22" t="s">
         <v>7972</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AC22" t="s">
         <v>7961</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="AD22" t="s">
         <v>7962</v>
       </c>
-      <c r="AD22" t="s">
+      <c r="AE22" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -31995,17 +32150,22 @@
       <c r="Y23" t="s">
         <v>7913</v>
       </c>
-      <c r="AA23" t="s">
+      <c r="AB23" t="s">
         <v>8004</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AC23" t="s">
         <v>7961</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AD23" t="s">
         <v>7962</v>
       </c>
-      <c r="AD23" t="s">
+      <c r="AE23" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -32081,17 +32241,22 @@
       <c r="Y24" t="s">
         <v>7913</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AB24" t="s">
         <v>8044</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AC24" t="s">
         <v>7961</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AD24" t="s">
         <v>7962</v>
       </c>
-      <c r="AD24" t="s">
+      <c r="AE24" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -32167,17 +32332,22 @@
       <c r="Y25" t="s">
         <v>7913</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AB25" t="s">
         <v>8065</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AC25" t="s">
         <v>7961</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AD25" t="s">
         <v>7962</v>
       </c>
-      <c r="AD25" t="s">
+      <c r="AE25" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -32253,17 +32423,22 @@
       <c r="Y26" t="s">
         <v>7913</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AB26" t="s">
         <v>8089</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AC26" t="s">
         <v>7961</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AD26" t="s">
         <v>7962</v>
       </c>
-      <c r="AD26" t="s">
+      <c r="AE26" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -32339,17 +32514,22 @@
       <c r="Y27" t="s">
         <v>7913</v>
       </c>
-      <c r="AA27" t="s">
+      <c r="AB27" t="s">
         <v>8004</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AC27" t="s">
         <v>7961</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AD27" t="s">
         <v>7962</v>
       </c>
-      <c r="AD27" t="s">
+      <c r="AE27" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -32425,17 +32605,22 @@
       <c r="Y28" t="s">
         <v>7913</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AB28" t="s">
         <v>8004</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>7961</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AD28" t="s">
         <v>7962</v>
       </c>
-      <c r="AD28" t="s">
+      <c r="AE28" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -32511,17 +32696,22 @@
       <c r="Y29" t="s">
         <v>7912</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AB29" t="s">
         <v>7960</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
         <v>7961</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AD29" t="s">
         <v>7962</v>
       </c>
-      <c r="AD29" t="s">
+      <c r="AE29" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -32597,17 +32787,22 @@
       <c r="Y30" t="s">
         <v>7913</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>8089</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
         <v>7961</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AD30" t="s">
         <v>7962</v>
       </c>
-      <c r="AD30" t="s">
+      <c r="AE30" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -32683,17 +32878,22 @@
       <c r="Y31" t="s">
         <v>7913</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AB31" t="s">
         <v>8044</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AC31" t="s">
         <v>7961</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AD31" t="s">
         <v>7962</v>
       </c>
-      <c r="AD31" t="s">
+      <c r="AE31" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -32769,17 +32969,22 @@
       <c r="Y32" t="s">
         <v>7910</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AB32" t="s">
         <v>8054</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>7961</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AD32" t="s">
         <v>7962</v>
       </c>
-      <c r="AD32" t="s">
+      <c r="AE32" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -32855,17 +33060,22 @@
       <c r="Y33" t="s">
         <v>7913</v>
       </c>
-      <c r="AA33" t="s">
+      <c r="AB33" t="s">
         <v>8044</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AC33" t="s">
         <v>7961</v>
       </c>
-      <c r="AC33" t="s">
+      <c r="AD33" t="s">
         <v>7962</v>
       </c>
-      <c r="AD33" t="s">
+      <c r="AE33" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -32941,17 +33151,22 @@
       <c r="Y34" t="s">
         <v>7916</v>
       </c>
-      <c r="AA34" t="s">
+      <c r="AB34" t="s">
         <v>7972</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AC34" t="s">
         <v>7961</v>
       </c>
-      <c r="AC34" t="s">
+      <c r="AD34" t="s">
         <v>7962</v>
       </c>
-      <c r="AD34" t="s">
+      <c r="AE34" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -33027,17 +33242,22 @@
       <c r="Y35" t="s">
         <v>7913</v>
       </c>
-      <c r="AA35" t="s">
+      <c r="AB35" t="s">
         <v>8130</v>
       </c>
-      <c r="AB35" t="s">
+      <c r="AC35" t="s">
         <v>7961</v>
       </c>
-      <c r="AC35" t="s">
+      <c r="AD35" t="s">
         <v>7962</v>
       </c>
-      <c r="AD35" t="s">
+      <c r="AE35" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -33116,17 +33336,22 @@
       <c r="Y36" t="s">
         <v>7913</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AB36" t="s">
         <v>7980</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AC36" t="s">
         <v>7961</v>
       </c>
-      <c r="AC36" t="s">
+      <c r="AD36" t="s">
         <v>7962</v>
       </c>
-      <c r="AD36" t="s">
+      <c r="AE36" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -33199,17 +33424,22 @@
       <c r="Y37" t="s">
         <v>7913</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AB37" t="s">
         <v>7972</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AC37" t="s">
         <v>7961</v>
       </c>
-      <c r="AC37" t="s">
+      <c r="AD37" t="s">
         <v>7962</v>
       </c>
-      <c r="AD37" t="s">
+      <c r="AE37" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -33285,17 +33515,22 @@
       <c r="Y38" t="s">
         <v>7910</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AB38" t="s">
         <v>8145</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AC38" t="s">
         <v>7961</v>
       </c>
-      <c r="AC38" t="s">
+      <c r="AD38" t="s">
         <v>7962</v>
       </c>
-      <c r="AD38" t="s">
+      <c r="AE38" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -33371,17 +33606,22 @@
       <c r="Y39" t="s">
         <v>7913</v>
       </c>
-      <c r="AA39" t="s">
+      <c r="AB39" t="s">
         <v>8044</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AC39" t="s">
         <v>7961</v>
       </c>
-      <c r="AC39" t="s">
+      <c r="AD39" t="s">
         <v>7962</v>
       </c>
-      <c r="AD39" t="s">
+      <c r="AE39" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -33457,17 +33697,22 @@
       <c r="Y40" t="s">
         <v>7913</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AB40" t="s">
         <v>8155</v>
       </c>
-      <c r="AB40" t="s">
+      <c r="AC40" t="s">
         <v>7961</v>
       </c>
-      <c r="AC40" t="s">
+      <c r="AD40" t="s">
         <v>7962</v>
       </c>
-      <c r="AD40" t="s">
+      <c r="AE40" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -33543,17 +33788,22 @@
       <c r="Y41" t="s">
         <v>7913</v>
       </c>
-      <c r="AA41" t="s">
+      <c r="AB41" t="s">
         <v>8004</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AC41" t="s">
         <v>7961</v>
       </c>
-      <c r="AC41" t="s">
+      <c r="AD41" t="s">
         <v>7962</v>
       </c>
-      <c r="AD41" t="s">
+      <c r="AE41" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -33629,17 +33879,22 @@
       <c r="Y42" t="s">
         <v>7913</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="AB42" t="s">
         <v>8004</v>
       </c>
-      <c r="AB42" t="s">
+      <c r="AC42" t="s">
         <v>7961</v>
       </c>
-      <c r="AC42" t="s">
+      <c r="AD42" t="s">
         <v>7962</v>
       </c>
-      <c r="AD42" t="s">
+      <c r="AE42" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -33715,17 +33970,22 @@
       <c r="Y43" t="s">
         <v>7913</v>
       </c>
-      <c r="AA43" t="s">
+      <c r="AB43" t="s">
         <v>8130</v>
       </c>
-      <c r="AB43" t="s">
+      <c r="AC43" t="s">
         <v>7961</v>
       </c>
-      <c r="AC43" t="s">
+      <c r="AD43" t="s">
         <v>7962</v>
       </c>
-      <c r="AD43" t="s">
+      <c r="AE43" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -33801,17 +34061,22 @@
       <c r="Y44" t="s">
         <v>7913</v>
       </c>
-      <c r="AA44" t="s">
+      <c r="AB44" t="s">
         <v>8044</v>
       </c>
-      <c r="AB44" t="s">
+      <c r="AC44" t="s">
         <v>7961</v>
       </c>
-      <c r="AC44" t="s">
+      <c r="AD44" t="s">
         <v>7962</v>
       </c>
-      <c r="AD44" t="s">
+      <c r="AE44" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -33887,17 +34152,22 @@
       <c r="Y45" t="s">
         <v>7913</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="AB45" t="s">
         <v>7960</v>
       </c>
-      <c r="AB45" t="s">
+      <c r="AC45" t="s">
         <v>7961</v>
       </c>
-      <c r="AC45" t="s">
+      <c r="AD45" t="s">
         <v>7962</v>
       </c>
-      <c r="AD45" t="s">
+      <c r="AE45" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -33973,17 +34243,22 @@
       <c r="Y46" t="s">
         <v>7913</v>
       </c>
-      <c r="AA46" t="s">
+      <c r="AB46" t="s">
         <v>7972</v>
       </c>
-      <c r="AB46" t="s">
+      <c r="AC46" t="s">
         <v>7961</v>
       </c>
-      <c r="AC46" t="s">
+      <c r="AD46" t="s">
         <v>7962</v>
       </c>
-      <c r="AD46" t="s">
+      <c r="AE46" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -34059,17 +34334,22 @@
       <c r="Y47" t="s">
         <v>7913</v>
       </c>
-      <c r="AA47" t="s">
+      <c r="AB47" t="s">
         <v>7980</v>
       </c>
-      <c r="AB47" t="s">
+      <c r="AC47" t="s">
         <v>7961</v>
       </c>
-      <c r="AC47" t="s">
+      <c r="AD47" t="s">
         <v>7962</v>
       </c>
-      <c r="AD47" t="s">
+      <c r="AE47" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -34145,17 +34425,22 @@
       <c r="Y48" t="s">
         <v>7912</v>
       </c>
-      <c r="AA48" t="s">
+      <c r="AB48" t="s">
         <v>7987</v>
       </c>
-      <c r="AB48" t="s">
+      <c r="AC48" t="s">
         <v>7961</v>
       </c>
-      <c r="AC48" t="s">
+      <c r="AD48" t="s">
         <v>7962</v>
       </c>
-      <c r="AD48" t="s">
+      <c r="AE48" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -34231,17 +34516,22 @@
       <c r="Y49" t="s">
         <v>7913</v>
       </c>
-      <c r="AA49" t="s">
+      <c r="AB49" t="s">
         <v>8004</v>
       </c>
-      <c r="AB49" t="s">
+      <c r="AC49" t="s">
         <v>7961</v>
       </c>
-      <c r="AC49" t="s">
+      <c r="AD49" t="s">
         <v>7962</v>
       </c>
-      <c r="AD49" t="s">
+      <c r="AE49" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -34314,17 +34604,22 @@
       <c r="Y50" t="s">
         <v>7913</v>
       </c>
-      <c r="AA50" t="s">
+      <c r="AB50" t="s">
         <v>8065</v>
       </c>
-      <c r="AB50" t="s">
+      <c r="AC50" t="s">
         <v>7961</v>
       </c>
-      <c r="AC50" t="s">
+      <c r="AD50" t="s">
         <v>7962</v>
       </c>
-      <c r="AD50" t="s">
+      <c r="AE50" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -34400,17 +34695,22 @@
       <c r="Y51" t="s">
         <v>7913</v>
       </c>
-      <c r="AA51" t="s">
+      <c r="AB51" t="s">
         <v>7972</v>
       </c>
-      <c r="AB51" t="s">
+      <c r="AC51" t="s">
         <v>7961</v>
       </c>
-      <c r="AC51" t="s">
+      <c r="AD51" t="s">
         <v>7962</v>
       </c>
-      <c r="AD51" t="s">
+      <c r="AE51" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -34486,17 +34786,22 @@
       <c r="Y52" t="s">
         <v>7913</v>
       </c>
-      <c r="AA52" t="s">
+      <c r="AB52" t="s">
         <v>7980</v>
       </c>
-      <c r="AB52" t="s">
+      <c r="AC52" t="s">
         <v>7961</v>
       </c>
-      <c r="AC52" t="s">
+      <c r="AD52" t="s">
         <v>7962</v>
       </c>
-      <c r="AD52" t="s">
+      <c r="AE52" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -34572,17 +34877,22 @@
       <c r="Y53" t="s">
         <v>7903</v>
       </c>
-      <c r="AA53" t="s">
+      <c r="AB53" t="s">
         <v>8004</v>
       </c>
-      <c r="AB53" t="s">
+      <c r="AC53" t="s">
         <v>7961</v>
       </c>
-      <c r="AC53" t="s">
+      <c r="AD53" t="s">
         <v>7962</v>
       </c>
-      <c r="AD53" t="s">
+      <c r="AE53" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -34658,17 +34968,22 @@
       <c r="Y54" t="s">
         <v>7913</v>
       </c>
-      <c r="AA54" t="s">
+      <c r="AB54" t="s">
         <v>8155</v>
       </c>
-      <c r="AB54" t="s">
+      <c r="AC54" t="s">
         <v>7961</v>
       </c>
-      <c r="AC54" t="s">
+      <c r="AD54" t="s">
         <v>7962</v>
       </c>
-      <c r="AD54" t="s">
+      <c r="AE54" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -34744,17 +35059,22 @@
       <c r="Y55" t="s">
         <v>7913</v>
       </c>
-      <c r="AA55" t="s">
+      <c r="AB55" t="s">
         <v>8054</v>
       </c>
-      <c r="AB55" t="s">
+      <c r="AC55" t="s">
         <v>7961</v>
       </c>
-      <c r="AC55" t="s">
+      <c r="AD55" t="s">
         <v>7962</v>
       </c>
-      <c r="AD55" t="s">
+      <c r="AE55" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -34830,17 +35150,22 @@
       <c r="Y56" t="s">
         <v>7913</v>
       </c>
-      <c r="AA56" t="s">
+      <c r="AB56" t="s">
         <v>8044</v>
       </c>
-      <c r="AB56" t="s">
+      <c r="AC56" t="s">
         <v>7961</v>
       </c>
-      <c r="AC56" t="s">
+      <c r="AD56" t="s">
         <v>7962</v>
       </c>
-      <c r="AD56" t="s">
+      <c r="AE56" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -34916,17 +35241,22 @@
       <c r="Y57" t="s">
         <v>7903</v>
       </c>
-      <c r="AA57" t="s">
+      <c r="AB57" t="s">
         <v>8229</v>
       </c>
-      <c r="AB57" t="s">
+      <c r="AC57" t="s">
         <v>7961</v>
       </c>
-      <c r="AC57" t="s">
+      <c r="AD57" t="s">
         <v>7962</v>
       </c>
-      <c r="AD57" t="s">
+      <c r="AE57" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -35002,17 +35332,22 @@
       <c r="Y58" t="s">
         <v>7913</v>
       </c>
-      <c r="AA58" t="s">
+      <c r="AB58" t="s">
         <v>7980</v>
       </c>
-      <c r="AB58" t="s">
+      <c r="AC58" t="s">
         <v>7961</v>
       </c>
-      <c r="AC58" t="s">
+      <c r="AD58" t="s">
         <v>7962</v>
       </c>
-      <c r="AD58" t="s">
+      <c r="AE58" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -35088,17 +35423,22 @@
       <c r="Y59" t="s">
         <v>7912</v>
       </c>
-      <c r="AA59" t="s">
+      <c r="AB59" t="s">
         <v>8054</v>
       </c>
-      <c r="AB59" t="s">
+      <c r="AC59" t="s">
         <v>7961</v>
       </c>
-      <c r="AC59" t="s">
+      <c r="AD59" t="s">
         <v>7962</v>
       </c>
-      <c r="AD59" t="s">
+      <c r="AE59" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -35174,17 +35514,22 @@
       <c r="Y60" t="s">
         <v>7913</v>
       </c>
-      <c r="AA60" t="s">
+      <c r="AB60" t="s">
         <v>8242</v>
       </c>
-      <c r="AB60" t="s">
+      <c r="AC60" t="s">
         <v>7961</v>
       </c>
-      <c r="AC60" t="s">
+      <c r="AD60" t="s">
         <v>7962</v>
       </c>
-      <c r="AD60" t="s">
+      <c r="AE60" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -35257,17 +35602,22 @@
       <c r="Y61" t="s">
         <v>7913</v>
       </c>
-      <c r="AA61" t="s">
+      <c r="AB61" t="s">
         <v>7987</v>
       </c>
-      <c r="AB61" t="s">
+      <c r="AC61" t="s">
         <v>7961</v>
       </c>
-      <c r="AC61" t="s">
+      <c r="AD61" t="s">
         <v>7962</v>
       </c>
-      <c r="AD61" t="s">
+      <c r="AE61" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -35343,17 +35693,22 @@
       <c r="Y62" t="s">
         <v>7912</v>
       </c>
-      <c r="AA62" t="s">
+      <c r="AB62" t="s">
         <v>8251</v>
       </c>
-      <c r="AB62" t="s">
+      <c r="AC62" t="s">
         <v>7961</v>
       </c>
-      <c r="AC62" t="s">
+      <c r="AD62" t="s">
         <v>7962</v>
       </c>
-      <c r="AD62" t="s">
+      <c r="AE62" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -35426,17 +35781,22 @@
       <c r="Y63" t="s">
         <v>7905</v>
       </c>
-      <c r="AA63" t="s">
+      <c r="AB63" t="s">
         <v>8044</v>
       </c>
-      <c r="AB63" t="s">
+      <c r="AC63" t="s">
         <v>7961</v>
       </c>
-      <c r="AC63" t="s">
+      <c r="AD63" t="s">
         <v>7962</v>
       </c>
-      <c r="AD63" t="s">
+      <c r="AE63" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -35512,17 +35872,22 @@
       <c r="Y64" t="s">
         <v>7913</v>
       </c>
-      <c r="AA64" t="s">
+      <c r="AB64" t="s">
         <v>8044</v>
       </c>
-      <c r="AB64" t="s">
+      <c r="AC64" t="s">
         <v>7961</v>
       </c>
-      <c r="AC64" t="s">
+      <c r="AD64" t="s">
         <v>7962</v>
       </c>
-      <c r="AD64" t="s">
+      <c r="AE64" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -35598,17 +35963,22 @@
       <c r="Y65" t="s">
         <v>7913</v>
       </c>
-      <c r="AA65" t="s">
+      <c r="AB65" t="s">
         <v>7960</v>
       </c>
-      <c r="AB65" t="s">
+      <c r="AC65" t="s">
         <v>7961</v>
       </c>
-      <c r="AC65" t="s">
+      <c r="AD65" t="s">
         <v>7962</v>
       </c>
-      <c r="AD65" t="s">
+      <c r="AE65" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -35684,17 +36054,22 @@
       <c r="Y66" t="s">
         <v>7910</v>
       </c>
-      <c r="AA66" t="s">
+      <c r="AB66" t="s">
         <v>7972</v>
       </c>
-      <c r="AB66" t="s">
+      <c r="AC66" t="s">
         <v>7961</v>
       </c>
-      <c r="AC66" t="s">
+      <c r="AD66" t="s">
         <v>7962</v>
       </c>
-      <c r="AD66" t="s">
+      <c r="AE66" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -35770,17 +36145,22 @@
       <c r="Y67" t="s">
         <v>7913</v>
       </c>
-      <c r="AA67" t="s">
+      <c r="AB67" t="s">
         <v>8130</v>
       </c>
-      <c r="AB67" t="s">
+      <c r="AC67" t="s">
         <v>7961</v>
       </c>
-      <c r="AC67" t="s">
+      <c r="AD67" t="s">
         <v>7962</v>
       </c>
-      <c r="AD67" t="s">
+      <c r="AE67" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -35856,17 +36236,22 @@
       <c r="Y68" t="s">
         <v>7903</v>
       </c>
-      <c r="AA68" t="s">
+      <c r="AB68" t="s">
         <v>8004</v>
       </c>
-      <c r="AB68" t="s">
+      <c r="AC68" t="s">
         <v>7961</v>
       </c>
-      <c r="AC68" t="s">
+      <c r="AD68" t="s">
         <v>7962</v>
       </c>
-      <c r="AD68" t="s">
+      <c r="AE68" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -35942,17 +36327,22 @@
       <c r="Y69" t="s">
         <v>7913</v>
       </c>
-      <c r="AA69" t="s">
+      <c r="AB69" t="s">
         <v>7980</v>
       </c>
-      <c r="AB69" t="s">
+      <c r="AC69" t="s">
         <v>7961</v>
       </c>
-      <c r="AC69" t="s">
+      <c r="AD69" t="s">
         <v>7962</v>
       </c>
-      <c r="AD69" t="s">
+      <c r="AE69" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -36028,17 +36418,22 @@
       <c r="Y70" t="s">
         <v>7913</v>
       </c>
-      <c r="AA70" t="s">
+      <c r="AB70" t="s">
         <v>8004</v>
       </c>
-      <c r="AB70" t="s">
+      <c r="AC70" t="s">
         <v>7961</v>
       </c>
-      <c r="AC70" t="s">
+      <c r="AD70" t="s">
         <v>7962</v>
       </c>
-      <c r="AD70" t="s">
+      <c r="AE70" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -36114,17 +36509,22 @@
       <c r="Y71" t="s">
         <v>7913</v>
       </c>
-      <c r="AA71" t="s">
+      <c r="AB71" t="s">
         <v>8293</v>
       </c>
-      <c r="AB71" t="s">
+      <c r="AC71" t="s">
         <v>7961</v>
       </c>
-      <c r="AC71" t="s">
+      <c r="AD71" t="s">
         <v>7962</v>
       </c>
-      <c r="AD71" t="s">
+      <c r="AE71" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -36200,17 +36600,22 @@
       <c r="Y72" t="s">
         <v>7913</v>
       </c>
-      <c r="AA72" t="s">
+      <c r="AB72" t="s">
         <v>8229</v>
       </c>
-      <c r="AB72" t="s">
+      <c r="AC72" t="s">
         <v>7961</v>
       </c>
-      <c r="AC72" t="s">
+      <c r="AD72" t="s">
         <v>7962</v>
       </c>
-      <c r="AD72" t="s">
+      <c r="AE72" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -36286,17 +36691,22 @@
       <c r="Y73" t="s">
         <v>7913</v>
       </c>
-      <c r="AA73" t="s">
+      <c r="AB73" t="s">
         <v>7980</v>
       </c>
-      <c r="AB73" t="s">
+      <c r="AC73" t="s">
         <v>7961</v>
       </c>
-      <c r="AC73" t="s">
+      <c r="AD73" t="s">
         <v>7962</v>
       </c>
-      <c r="AD73" t="s">
+      <c r="AE73" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -36372,17 +36782,22 @@
       <c r="Y74" t="s">
         <v>7913</v>
       </c>
-      <c r="AA74" t="s">
+      <c r="AB74" t="s">
         <v>7960</v>
       </c>
-      <c r="AB74" t="s">
+      <c r="AC74" t="s">
         <v>7961</v>
       </c>
-      <c r="AC74" t="s">
+      <c r="AD74" t="s">
         <v>7962</v>
       </c>
-      <c r="AD74" t="s">
+      <c r="AE74" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -36458,17 +36873,22 @@
       <c r="Y75" t="s">
         <v>7912</v>
       </c>
-      <c r="AA75" t="s">
+      <c r="AB75" t="s">
         <v>8044</v>
       </c>
-      <c r="AB75" t="s">
+      <c r="AC75" t="s">
         <v>7961</v>
       </c>
-      <c r="AC75" t="s">
+      <c r="AD75" t="s">
         <v>7962</v>
       </c>
-      <c r="AD75" t="s">
+      <c r="AE75" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -36544,17 +36964,22 @@
       <c r="Y76" t="s">
         <v>7913</v>
       </c>
-      <c r="AA76" t="s">
+      <c r="AB76" t="s">
         <v>8229</v>
       </c>
-      <c r="AB76" t="s">
+      <c r="AC76" t="s">
         <v>7961</v>
       </c>
-      <c r="AC76" t="s">
+      <c r="AD76" t="s">
         <v>7962</v>
       </c>
-      <c r="AD76" t="s">
+      <c r="AE76" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -36630,17 +37055,22 @@
       <c r="Y77" t="s">
         <v>7913</v>
       </c>
-      <c r="AA77" t="s">
+      <c r="AB77" t="s">
         <v>8044</v>
       </c>
-      <c r="AB77" t="s">
+      <c r="AC77" t="s">
         <v>7961</v>
       </c>
-      <c r="AC77" t="s">
+      <c r="AD77" t="s">
         <v>7962</v>
       </c>
-      <c r="AD77" t="s">
+      <c r="AE77" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -36716,17 +37146,22 @@
       <c r="Y78" t="s">
         <v>7912</v>
       </c>
-      <c r="AA78" t="s">
+      <c r="AB78" t="s">
         <v>7987</v>
       </c>
-      <c r="AB78" t="s">
+      <c r="AC78" t="s">
         <v>7961</v>
       </c>
-      <c r="AC78" t="s">
+      <c r="AD78" t="s">
         <v>7962</v>
       </c>
-      <c r="AD78" t="s">
+      <c r="AE78" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -36802,17 +37237,22 @@
       <c r="Y79" t="s">
         <v>7903</v>
       </c>
-      <c r="AA79" t="s">
+      <c r="AB79" t="s">
         <v>8044</v>
       </c>
-      <c r="AB79" t="s">
+      <c r="AC79" t="s">
         <v>7961</v>
       </c>
-      <c r="AC79" t="s">
+      <c r="AD79" t="s">
         <v>7962</v>
       </c>
-      <c r="AD79" t="s">
+      <c r="AE79" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -36888,17 +37328,22 @@
       <c r="Y80" t="s">
         <v>7910</v>
       </c>
-      <c r="AA80" t="s">
+      <c r="AB80" t="s">
         <v>8004</v>
       </c>
-      <c r="AB80" t="s">
+      <c r="AC80" t="s">
         <v>7961</v>
       </c>
-      <c r="AC80" t="s">
+      <c r="AD80" t="s">
         <v>7962</v>
       </c>
-      <c r="AD80" t="s">
+      <c r="AE80" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -36974,17 +37419,22 @@
       <c r="Y81" t="s">
         <v>7913</v>
       </c>
-      <c r="AA81" t="s">
+      <c r="AB81" t="s">
         <v>8004</v>
       </c>
-      <c r="AB81" t="s">
+      <c r="AC81" t="s">
         <v>7961</v>
       </c>
-      <c r="AC81" t="s">
+      <c r="AD81" t="s">
         <v>7962</v>
       </c>
-      <c r="AD81" t="s">
+      <c r="AE81" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -37060,17 +37510,22 @@
       <c r="Y82" t="s">
         <v>7913</v>
       </c>
-      <c r="AA82" t="s">
+      <c r="AB82" t="s">
         <v>8341</v>
       </c>
-      <c r="AB82" t="s">
+      <c r="AC82" t="s">
         <v>7961</v>
       </c>
-      <c r="AC82" t="s">
+      <c r="AD82" t="s">
         <v>7962</v>
       </c>
-      <c r="AD82" t="s">
+      <c r="AE82" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -37146,17 +37601,22 @@
       <c r="Y83" t="s">
         <v>7913</v>
       </c>
-      <c r="AA83" t="s">
+      <c r="AB83" t="s">
         <v>8054</v>
       </c>
-      <c r="AB83" t="s">
+      <c r="AC83" t="s">
         <v>7961</v>
       </c>
-      <c r="AC83" t="s">
+      <c r="AD83" t="s">
         <v>7962</v>
       </c>
-      <c r="AD83" t="s">
+      <c r="AE83" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -37232,17 +37692,22 @@
       <c r="Y84" t="s">
         <v>7913</v>
       </c>
-      <c r="AA84" t="s">
+      <c r="AB84" t="s">
         <v>8065</v>
       </c>
-      <c r="AB84" t="s">
+      <c r="AC84" t="s">
         <v>7961</v>
       </c>
-      <c r="AC84" t="s">
+      <c r="AD84" t="s">
         <v>7962</v>
       </c>
-      <c r="AD84" t="s">
+      <c r="AE84" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -37318,17 +37783,22 @@
       <c r="Y85" t="s">
         <v>7913</v>
       </c>
-      <c r="AA85" t="s">
+      <c r="AB85" t="s">
         <v>7972</v>
       </c>
-      <c r="AB85" t="s">
+      <c r="AC85" t="s">
         <v>7961</v>
       </c>
-      <c r="AC85" t="s">
+      <c r="AD85" t="s">
         <v>7962</v>
       </c>
-      <c r="AD85" t="s">
+      <c r="AE85" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -37401,17 +37871,22 @@
       <c r="Y86" t="s">
         <v>7913</v>
       </c>
-      <c r="AA86" t="s">
+      <c r="AB86" t="s">
         <v>8229</v>
       </c>
-      <c r="AB86" t="s">
+      <c r="AC86" t="s">
         <v>7961</v>
       </c>
-      <c r="AC86" t="s">
+      <c r="AD86" t="s">
         <v>7962</v>
       </c>
-      <c r="AD86" t="s">
+      <c r="AE86" t="s">
         <v>7963</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -37530,12 +38005,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
+      <c r="AC87" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD87" t="inlineStr">
+      <c r="AE87" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -37543,6 +38018,11 @@
       <c r="Z87" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/_vmhz17RjUJqJQ</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -37662,12 +38142,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
+      <c r="AC88" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD88" t="inlineStr">
+      <c r="AE88" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -37675,6 +38155,11 @@
       <c r="Z88" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/wMgQUTpqNCuwjg</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -37794,12 +38279,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
+      <c r="AC89" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD89" t="inlineStr">
+      <c r="AE89" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -37807,6 +38292,11 @@
       <c r="Z89" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/o6IH59mUXAby0Q</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -37926,12 +38416,12 @@
           <t xml:space="preserve">Силикон</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
+      <c r="AC90" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD90" t="inlineStr">
+      <c r="AE90" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -37939,6 +38429,11 @@
       <c r="Z90" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/Io87sSjfuT_16A</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -38058,12 +38553,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
+      <c r="AC91" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD91" t="inlineStr">
+      <c r="AE91" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -38071,6 +38566,11 @@
       <c r="Z91" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/3w2RoL4oPjPrRA</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -38190,12 +38690,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
+      <c r="AC92" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD92" t="inlineStr">
+      <c r="AE92" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -38203,6 +38703,11 @@
       <c r="Z92" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/QFgv2fVT-QGmDw</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -38322,12 +38827,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
+      <c r="AC93" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD93" t="inlineStr">
+      <c r="AE93" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -38335,6 +38840,11 @@
       <c r="Z93" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/gxdIEZNTp_UERw</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -38454,12 +38964,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
+      <c r="AC94" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD94" t="inlineStr">
+      <c r="AE94" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -38467,6 +38977,11 @@
       <c r="Z94" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/vJULBAjDHfnVBg</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -38586,12 +39101,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
+      <c r="AC95" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD95" t="inlineStr">
+      <c r="AE95" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -38599,6 +39114,11 @@
       <c r="Z95" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/PGuf74v2ZUNyUA</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -38718,12 +39238,12 @@
           <t xml:space="preserve">Браслет</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
+      <c r="AC96" t="inlineStr">
         <is>
           <t xml:space="preserve">Электроника С Гарантией</t>
         </is>
       </c>
-      <c r="AD96" t="inlineStr">
+      <c r="AE96" t="inlineStr">
         <is>
           <t xml:space="preserve">golodnovewan@yandex.ru</t>
         </is>
@@ -38731,6 +39251,11 @@
       <c r="Z96" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/S46l-rAlfcu3NQ</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>
@@ -77832,27 +78357,32 @@
       <c r="P2" s="7" t="s">
         <v>7943</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="T2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="U2" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="V2" s="7" t="s">
         <v>7950</v>
       </c>
-      <c r="V2" s="7" t="s">
+      <c r="W2" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">URL видеофайла</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Способ доставки</t>
+        </is>
+      </c>
     </row>
     <row r="3" s="6" customFormat="true" ht="45" customHeight="true">
       <c r="A3" s="6" t="s">
@@ -77908,6 +78438,11 @@
           <t xml:space="preserve">Необязательный</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Необязательный</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -78005,24 +78540,29 @@
       <c r="O5" t="s">
         <v>87</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>7962</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
         <v>8130</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5" t="s">
         <v>7961</v>
       </c>
-      <c r="U5" t="s">
+      <c r="V5" t="s">
         <v>8420</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>7963</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">https://disk.yandex.ru/i/fmCxUxBaEehBog</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
     </row>

--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -39259,6 +39259,1376 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_Cartier_Panthere_steel_27</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/hxbZ0ksH/i3-Cartier-Panthere-steel-27-0.jpg | https://i.ibb.co/SXMfFyr0/i3-Cartier-Panthere-steel-27-1.jpg | https://i.ibb.co/kVQRWNFx/i3-Cartier-Panthere-steel-27-2.jpg | https://i.ibb.co/B2n6X3hR/i3-Cartier-Panthere-steel-27-3.jpg | https://i.ibb.co/844WJH6y/i3-Cartier-Panthere-steel-27-4.jpg | https://i.ibb.co/tPqynZWR/i3-Cartier-Panthere-steel-27-5.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Смотрят на руку — Cartier Panthere сталь 27 мм</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Cartier Panthere — белый, сталь 27 мм&lt;br&gt;&lt;br&gt;Квадратный корпус и мягкие звенья ложатся на запястье как браслет — часы, которые носят каждый день и не снимают на вечер. Модель из тех, что узнают без логотипа на виду.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь, 27 мм, квадратный&lt;br&gt;▫️ Циферблат: белый, римские цифры&lt;br&gt;▫️ Браслет: сталь&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier panthere сталь, часы квадратные женские, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15500</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Panthere 27</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/J7pZVoRxK4Dmbw</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_Cartier_Panthere_gold_27</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/Z1V0tCxh/i3-Cartier-Panthere-gold-27-0.jpg | https://i.ibb.co/d09GCPXh/i3-Cartier-Panthere-gold-27-1.jpg | https://i.ibb.co/1YNXVGyQ/i3-Cartier-Panthere-gold-27-2.jpg | https://i.ibb.co/twsFx7VW/i3-Cartier-Panthere-gold-27-3.jpg | https://i.ibb.co/Xr9B27ns/i3-Cartier-Panthere-gold-27-4.jpg | https://i.ibb.co/vxhM3Z6V/i3-Cartier-Panthere-gold-27-5.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тёплое золото — Cartier Panthere 27 мм женские</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Cartier Panthere — белый, золото 27 мм&lt;br&gt;&lt;br&gt;Золотистый корпус и белый циферблат — вариант, который заметнее стального, но не превращается в украшение напоказ. Хорошо смотрится рядом с тонкими браслетами и кольцами.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: цвет золота, 27 мм, квадратный&lt;br&gt;▫️ Циферблат: белый, римские цифры&lt;br&gt;▫️ Браслет: цвет золота&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier panthere золото, золотые часы женские, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15500</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Panthere 27</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/ERARTcNkW7gRuw</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_Cartier_Panthere_steel_diamonds_27</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/Q3LJzZh6/i3-Cartier-Panthere-steel-diamonds-27-0.jpg | https://i.ibb.co/xtPjVF37/i3-Cartier-Panthere-steel-diamonds-27-1.jpg | https://i.ibb.co/MxMHDryr/i3-Cartier-Panthere-steel-diamonds-27-2.jpg | https://i.ibb.co/wr2Xpw6C/i3-Cartier-Panthere-steel-diamonds-27-3.jpg | https://i.ibb.co/Z6Q20rrC/i3-Cartier-Panthere-steel-diamonds-27-4.jpg | https://i.ibb.co/4gN9TyXL/i3-Cartier-Panthere-steel-diamonds-27-5.jpg</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Камни по безелю — Cartier Panthere сталь</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Cartier Panthere — белый, камни по безелю&lt;br&gt;&lt;br&gt;Камни по рамке добавляют блеска ровно столько, чтобы часы читались вечером, но не мешали днём. База при этом строгая — сталь и белый циферблат с римскими цифрами. Такие часы одинаково уместны на работе и на ужине, и их не нужно менять под наряд.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь, камни по безелю, 27 мм&lt;br&gt;▫️ Циферблат: белый, римские цифры&lt;br&gt;▫️ Браслет: сталь&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier panthere камни, часы с камнями женские, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16500</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Panthere 27</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/jtAjujrR4UZs1A</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_Rolex_Datejust36_green_twotone</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/2YnRZhJ4/i3-Rolex-Datejust36-green-twotone-0.jpg | https://i.ibb.co/5hSsb4K6/i3-Rolex-Datejust36-green-twotone-1.jpg | https://i.ibb.co/pBw0tTzg/i3-Rolex-Datejust36-green-twotone-2.jpg | https://i.ibb.co/Y7JJ3GVN/i3-Rolex-Datejust36-green-twotone-3.jpg | https://i.ibb.co/bjdhhj1Z/i3-Rolex-Datejust36-green-twotone-4.jpg | https://i.ibb.co/1fVfqpZX/i3-Rolex-Datejust36-green-twotone-5.jpg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Rolex Datejust 36 зелёный сталь золото</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Rolex Datejust 36 — зелёный, сталь и золото&lt;br&gt;&lt;br&gt;Зелёный циферблат на двухцветном браслете — редкое сочетание, которое видно с метра. Размер 36 мм подходит и мужской, и крупной женской руке.&lt;br&gt;&lt;br&gt;▫️ Механизм: механический с автоподзаводом&lt;br&gt;▫️ Корпус: сталь и цвет золота, 36 мм, рифлёный безель&lt;br&gt;▫️ Циферблат: зелёный, окно даты&lt;br&gt;▫️ Браслет: Jubilee, сталь и золото&lt;br&gt;▫️ Функции: дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы rolex мужские, rolex datejust зелёный, часы сталь золото, наручные часы механика</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16900</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex Datejust 36</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/N62j7VqsNFKQxQ</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_Rolex_Datejust31_champagne_twotone</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/C5Sx8dvL/i3-Rolex-Datejust31-champagne-twotone-0.jpg | https://i.ibb.co/fzb2p7p7/i3-Rolex-Datejust31-champagne-twotone-1.jpg | https://i.ibb.co/fd2K00yH/i3-Rolex-Datejust31-champagne-twotone-2.jpg | https://i.ibb.co/sdQ5fgJR/i3-Rolex-Datejust31-champagne-twotone-3.jpg | https://i.ibb.co/Xg0QY1y/i3-Rolex-Datejust31-champagne-twotone-4.jpg</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Шампань и золото — Rolex Datejust 31 мм</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Rolex Datejust 31 — шампань, сталь и золото&lt;br&gt;&lt;br&gt;Рифлёный безель и браслет Jubilee — классика, которую считывают мгновенно. Размер выбран так, чтобы часы не спорили с манжетой и одинаково сидели с рубашкой и с трикотажем.&lt;br&gt;&lt;br&gt;▫️ Механизм: механический с автоподзаводом&lt;br&gt;▫️ Корпус: сталь и цвет золота, 31 мм, рифлёный безель&lt;br&gt;▫️ Циферблат: цвет шампанского, окно даты&lt;br&gt;▫️ Браслет: Jubilee, сталь и золото&lt;br&gt;▫️ Функции: дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы rolex женские, rolex datejust 31, часы сталь золото, наручные часы механика</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16500</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex Datejust 31</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/scp2_bx7hnKRTA</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_Rolex_Datejust31_steel_diamonds</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/HLvw41tG/i3-Rolex-Datejust31-steel-diamonds-0.jpg | https://i.ibb.co/jdCTNKR/i3-Rolex-Datejust31-steel-diamonds-1.jpg | https://i.ibb.co/Z1K4380G/i3-Rolex-Datejust31-steel-diamonds-2.jpg | https://i.ibb.co/QF5rpKzM/i3-Rolex-Datejust31-steel-diamonds-3.jpg | https://i.ibb.co/rKZbJyyf/i3-Rolex-Datejust31-steel-diamonds-4.jpg</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Камни на метках — Rolex Datejust 31 сталь</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Rolex Datejust 31 — серебристый, камни на метках&lt;br&gt;&lt;br&gt;Светлый циферблат с камнями вместо часовых меток — вечерний вариант на каждый день. Стальной браслет держит образ строгим, блеск идёт только от циферблата.&lt;br&gt;&lt;br&gt;▫️ Механизм: механический с автоподзаводом&lt;br&gt;▫️ Корпус: сталь, 31 мм, рифлёный безель&lt;br&gt;▫️ Циферблат: серебристый, камни на метках, окно даты&lt;br&gt;▫️ Браслет: Jubilee, сталь&lt;br&gt;▫️ Функции: дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы rolex женские, rolex datejust сталь, часы с камнями женские, наручные часы механика</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16500</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серебряный</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex Datejust 31</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/6nsJaLMAXVosyg</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_AX_diver_steel_white</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/LXxy86qM/i3-AX-diver-steel-white-0.jpg | https://i.ibb.co/5hY3C4gr/i3-AX-diver-steel-white-1.jpg | https://i.ibb.co/MkWhdT4J/i3-AX-diver-steel-white-2.jpg | https://i.ibb.co/ccqBNyDG/i3-AX-diver-steel-white-3.jpg | https://i.ibb.co/zHLcHVBp/i3-AX-diver-steel-white-4.jpg | https://i.ibb.co/d0W8Lk9x/i3-AX-diver-steel-white-5.jpg</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Холодная сталь — Armani Exchange дайвер белый</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Armani Exchange Diver — белый, сталь&lt;br&gt;&lt;br&gt;Белый циферблат и стальной браслет — светлая версия дайвера, которая летом смотрится легче тёмных. Крупные метки видно даже боковым зрением, а безель вращается с чётким щелчком. Такие часы берут как первые «серьёзные» — носить каждый день и не бояться.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь, вращающийся безель&lt;br&gt;▫️ Циферблат: белый, крупные светящиеся метки&lt;br&gt;▫️ Браслет: сталь&lt;br&gt;▫️ Функции: дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы armani exchange, armani дайвер, белые часы мужские, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange Diver</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Календарь</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/vP_r3YpX6kjl0w</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_AX_chrono_rose_blue</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/B5sVFCbP/i3-AX-chrono-rose-blue-0.jpg | https://i.ibb.co/4gZfJF9b/i3-AX-chrono-rose-blue-1.jpg | https://i.ibb.co/5h9H2rkz/i3-AX-chrono-rose-blue-2.jpg | https://i.ibb.co/23H55RFm/i3-AX-chrono-rose-blue-3.jpg | https://i.ibb.co/84dCzYVL/i3-AX-chrono-rose-blue-4.jpg | https://i.ibb.co/S4XDQy42/i3-AX-chrono-rose-blue-5.jpg</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Armani Exchange хронограф синий кожа</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Armani Exchange Chronograph — синий, розовое золото&lt;br&gt;&lt;br&gt;Корпус цвета розового золота и синий циферблат на кожаном ремешке — вариант под рубашку, а не под спорт. Тонкий профиль уходит под манжету без усилий.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: цвет розового золота&lt;br&gt;▫️ Циферблат: синий, три счётчика хронографа&lt;br&gt;▫️ Ремешок: синяя кожа&lt;br&gt;▫️ Функции: хронограф, дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы armani exchange, armani хронограф, часы на кожаном ремешке, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange Chronograph</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Календарь | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/bI47jmQpDJJxYw</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_AX_chrono_black_leather</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/5xgDKPkM/i3-AX-chrono-black-leather-0.jpg | https://i.ibb.co/ns7myrVR/i3-AX-chrono-black-leather-1.jpg | https://i.ibb.co/0Wk5CJY/i3-AX-chrono-black-leather-2.jpg | https://i.ibb.co/k2nLRtwV/i3-AX-chrono-black-leather-3.jpg | https://i.ibb.co/nsSmswzT/i3-AX-chrono-black-leather-4.jpg | https://i.ibb.co/B2CmDh5g/i3-AX-chrono-black-leather-5.jpg</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Строго и дорого — Armani Exchange хронограф</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Armani Exchange Chronograph — чёрный&lt;br&gt;&lt;br&gt;Чёрный циферблат, тёмный корпус и коричневая кожа — самое спокойное сочетание из линейки. Такие часы не спорят ни с костюмом, ни с курткой.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: тёмный металл&lt;br&gt;▫️ Циферблат: чёрный, три счётчика хронографа&lt;br&gt;▫️ Ремешок: коричневая кожа&lt;br&gt;▫️ Функции: хронограф, дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы armani exchange, armani хронограф чёрный, часы кожаный ремешок, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange Chronograph</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Календарь | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/REhOtG3Cx2SopQ</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i0918_Diesel_MrDaddy_gold</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/MkPj55gv/i3-Diesel-Mr-Daddy-gold-0.jpg | https://i.ibb.co/Ngw7smGJ/i3-Diesel-Mr-Daddy-gold-1.jpg | https://i.ibb.co/6JqvB233/i3-Diesel-Mr-Daddy-gold-2.jpg | https://i.ibb.co/SwHPRWv4/i3-Diesel-Mr-Daddy-gold-3.jpg | https://i.ibb.co/bjtcNzVs/i3-Diesel-Mr-Daddy-gold-4.jpg</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой гигант — часы Diesel Mr Daddy 2.0</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Diesel Mr Daddy 2.0 — золотой&lt;br&gt;&lt;br&gt;Огромный золотистый корпус и четыре циферблата — часы, которые невозможно не заметить. Носят их с худи и курткой, под рубашку такие не прячут.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: цвет золота, крупный размер&lt;br&gt;▫️ Циферблат: золотистый, четыре дополнительных циферблата, окно даты&lt;br&gt;▫️ Браслет: цвет золота&lt;br&gt;▫️ Функции: дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы diesel мужские, diesel mr daddy, крупные часы золото, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16500</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diesel</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diesel Mr Daddy 2-0</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Календарь</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/5urIwTE7sDiwDw</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K5:K1048576">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -40629,6 +40629,1376 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_Cartier_Panthere_steel_22_diamonds</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/DP9CkGrH/i3-Cartier-Panthere-steel-22-diamonds-0.jpg | https://i.ibb.co/cX8RGVs3/i3-Cartier-Panthere-steel-22-diamonds-1.jpg | https://i.ibb.co/jPtw5s5Y/i3-Cartier-Panthere-steel-22-diamonds-2.jpg | https://i.ibb.co/SXQYCnGz/i3-Cartier-Panthere-steel-22-diamonds-3.jpg | https://i.ibb.co/CrRd4wL/i3-Cartier-Panthere-steel-22-diamonds-4.jpg | https://i.ibb.co/CK59gGj0/i3-Cartier-Panthere-steel-22-diamonds-5.jpg</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блеск без лишнего — Cartier Panthere с камнями</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Cartier Panthere — белый, сталь 22 мм, камни по безелю&lt;br&gt;&lt;br&gt;Тонкая россыпь камней по рамке даёт ровно столько блеска, чтобы часы были заметны вечером и не выглядели вычурно днём. Стальной браслет из мягких звеньев ложится на запястье, как украшение, а не как «прибор».&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь, 22 мм, камни по безелю, квадратный&lt;br&gt;▫️ Циферблат: белый, римские цифры&lt;br&gt;▫️ Браслет: сталь&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier panthere камни, маленькие часы женские, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15500</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Panthere 22</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/w7Szgu7B2cewgg</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_Cartier_Panthere_gold_27_diamonds</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/ZRRFbHhS/i3-Cartier-Panthere-gold-27-diamonds-0.jpg | https://i.ibb.co/1fXjz9bk/i3-Cartier-Panthere-gold-27-diamonds-1.jpg | https://i.ibb.co/RGB7rhf0/i3-Cartier-Panthere-gold-27-diamonds-2.jpg | https://i.ibb.co/YFZhs8Vm/i3-Cartier-Panthere-gold-27-diamonds-3.jpg | https://i.ibb.co/24n3dwW/i3-Cartier-Panthere-gold-27-diamonds-4.jpg | https://i.ibb.co/5XQFdVs2/i3-Cartier-Panthere-gold-27-diamonds-5.jpg</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золото и камни — Cartier Panthere 27 мм</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Cartier Panthere — белый, золото 27 мм, камни по безелю&lt;br&gt;&lt;br&gt;Золотистый корпус, камни по рамке и белый циферблат с римскими цифрами — вариант, который читается как «дорогая вещь» с первого взгляда. Размер 27 мм заметнее компактной версии, но остаётся женским и аккуратным.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: цвет золота, 27 мм, камни по безелю, квадратный&lt;br&gt;▫️ Циферблат: белый, римские цифры&lt;br&gt;▫️ Браслет: цвет золота&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier panthere золото, золотые часы с камнями, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16500</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Panthere 27</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/Gh-Fq0zhV_i65A</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_Cartier_Panthere_twotone_diamonds</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/6MgqdW5/i3-Cartier-Panthere-twotone-diamonds-0.jpg | https://i.ibb.co/mCN1xdcw/i3-Cartier-Panthere-twotone-diamonds-1.jpg | https://i.ibb.co/mVTbjVHB/i3-Cartier-Panthere-twotone-diamonds-2.jpg | https://i.ibb.co/27DrWFzM/i3-Cartier-Panthere-twotone-diamonds-3.jpg | https://i.ibb.co/1t8Rwh0d/i3-Cartier-Panthere-twotone-diamonds-4.jpg | https://i.ibb.co/G3b7j0Xj/i3-Cartier-Panthere-twotone-diamonds-5.jpg</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Два металла — Cartier Panthere с камнями</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Cartier Panthere — белый, сталь и золото, камни по безелю&lt;br&gt;&lt;br&gt;Двухцветный браслет сочетается и с серебром, и с золотом в украшениях — не придётся выбирать под что надевать. Компактный корпус с камнями по рамке подходит тонкому запястью, где крупные часы смотрятся чужими.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь с золотистой отделкой, камни по безелю, квадратный&lt;br&gt;▫️ Циферблат: белый, римские цифры&lt;br&gt;▫️ Браслет: сталь с золотистыми звеньями&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы cartier женские, cartier panthere сталь золото, часы с камнями женские, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15500</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Белый</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartier Panthere 22</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/MEQRj-06Gc_AMQ</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_Rolex_Datejust31_champagne_fluted</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/fdbLkjMy/i3-Rolex-Datejust31-champagne-fluted-0.jpg | https://i.ibb.co/VcNjZKZS/i3-Rolex-Datejust31-champagne-fluted-1.jpg | https://i.ibb.co/V0JGn1KG/i3-Rolex-Datejust31-champagne-fluted-2.jpg | https://i.ibb.co/cSRSGVbF/i3-Rolex-Datejust31-champagne-fluted-3.jpg | https://i.ibb.co/ZzGtpRXp/i3-Rolex-Datejust31-champagne-fluted-4.jpg</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Rolex Datejust 31 шампань сталь золото</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Rolex Datejust 31 — шампань, сталь и золото, рифлёный безель&lt;br&gt;&lt;br&gt;Циферблат цвета шампанского и рифлёный безель на двухцветном браслете Jubilee — самая тёплая версия Datejust, которая работает с любым тоном кожи. Размер 31 мм рассчитан на небольшое и среднее запястье.&lt;br&gt;&lt;br&gt;▫️ Механизм: механический с автоподзаводом&lt;br&gt;▫️ Корпус: сталь и цвет золота, 31 мм, рифлёный безель&lt;br&gt;▫️ Циферблат: цвет шампанского, окно даты&lt;br&gt;▫️ Браслет: Jubilee, сталь и золото&lt;br&gt;▫️ Функции: дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы rolex женские, rolex datejust 31 шампань, часы сталь золото, наручные часы механика</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16500</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Золотой</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex Datejust 31</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/Ig3szrq3-VR1Ww</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_Rolex_Datejust31_black_diamond_bezel</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/fdCB5t3z/i3-Rolex-Datejust31-black-diamond-bezel-0.jpg | https://i.ibb.co/Lh60FYQr/i3-Rolex-Datejust31-black-diamond-bezel-1.jpg | https://i.ibb.co/PZ8wh1FN/i3-Rolex-Datejust31-black-diamond-bezel-2.jpg | https://i.ibb.co/svdvLpZh/i3-Rolex-Datejust31-black-diamond-bezel-3.jpg | https://i.ibb.co/zVQ7ZrD7/i3-Rolex-Datejust31-black-diamond-bezel-4.jpg</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный с камнями — Rolex Datejust 31 мм</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Rolex Datejust 31 — чёрный, камни на метках и безеле&lt;br&gt;&lt;br&gt;Чёрный циферблат с камнями вместо меток и безель, обсыпанный камнями, на двухцветном Jubilee — вечерний вариант, который не приходится менять на дневной. Контраст тёмного циферблата и золотых звеньев виден даже в полумраке.&lt;br&gt;&lt;br&gt;▫️ Механизм: механический с автоподзаводом&lt;br&gt;▫️ Корпус: сталь и цвет золота, 31 мм, камни по безелю&lt;br&gt;▫️ Циферблат: чёрный, камни на метках, окно даты&lt;br&gt;▫️ Браслет: Jubilee, сталь и золото&lt;br&gt;▫️ Функции: дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы rolex женские, rolex datejust 31 камни, часы с камнями женские, наручные часы механика</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17500</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolex Datejust 31</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Женские</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Механические</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Автоподзавод | Календарь</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/PB25gUBdXbkO5w</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_AX_chrono_green</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/xSYgX8Hh/i3-AX-chrono-green-0.jpg | https://i.ibb.co/JWLQP1dR/i3-AX-chrono-green-1.jpg | https://i.ibb.co/8Lfmf8zt/i3-AX-chrono-green-2.jpg | https://i.ibb.co/d4zQTCZn/i3-AX-chrono-green-3.jpg | https://i.ibb.co/nM9fj9SC/i3-AX-chrono-green-4.jpg | https://i.ibb.co/9kJG4TX5/i3-AX-chrono-green-5.jpg</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мятный зелёный — Armani Exchange хронограф</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Armani Exchange Chronograph — зелёный, сталь&lt;br&gt;&lt;br&gt;Светлый зелёный циферблат и ремешок в тон — часы, которые выбиваются из чёрно-синего большинства и при этом остаются спокойными. Хорошо смотрятся с белой рубашкой и с футболкой, летом заметно освежают образ.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь&lt;br&gt;▫️ Циферблат: зелёный, три счётчика хронографа, окно даты&lt;br&gt;▫️ Ремешок: зелёная кожа&lt;br&gt;▫️ Функции: хронограф, дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы armani exchange, armani хронограф зелёный, часы на кожаном ремешке, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange Chronograph</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Календарь | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/7RGQA_BR9sf7sw</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_AX_chrono_steel_blue_leather</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/zVCTv9Pw/i3-AX-chrono-steel-blue-leather-0.jpg | https://i.ibb.co/7tzs68Bz/i3-AX-chrono-steel-blue-leather-1.jpg | https://i.ibb.co/tMSmx89Z/i3-AX-chrono-steel-blue-leather-2.jpg | https://i.ibb.co/pBZxzyZJ/i3-AX-chrono-steel-blue-leather-3.jpg | https://i.ibb.co/b5Xf1q2H/i3-AX-chrono-steel-blue-leather-4.jpg | https://i.ibb.co/gbZ6rWQf/i3-AX-chrono-steel-blue-leather-5.jpg</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий с секретом — часы Armani Exchange</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Armani Exchange Classic — синий, сталь&lt;br&gt;&lt;br&gt;Глубокий синий циферблат с тремя малыми циферблатами, два из них с открытым фоном — деталь, которую замечают, когда часы уже поймали взгляд. Синяя кожа и стальной корпус делают их подходящими и под пиджак, и под свитер.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь&lt;br&gt;▫️ Циферблат: синий, три малых циферблата&lt;br&gt;▫️ Ремешок: синяя кожа&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы armani exchange, armani синий циферблат, часы на кожаном ремешке, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange Classic</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кожаный</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/ZSyutJ9qfCZmjQ</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_AX_gold_blue_brown_leather</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://i.ibb.co/8D0GQS1m/i3-AX-gold-blue-brown-leather-0.jpg | https://i.ibb.co/spdDK6Cp/i3-AX-gold-blue-brown-leather-1.jpg | https://i.ibb.co/1Yzw9P23/i3-AX-gold-blue-brown-leather-2.jpg | https://i.ibb.co/v91cZ6x/i3-AX-gold-blue-brown-leather-3.jpg | https://i.ibb.co/Wv0mdLhv/i3-AX-gold-blue-brown-leather-4.jpg | https://i.ibb.co/JWLWvRd4/i3-AX-gold-blue-brown-leather-5.jpg</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Armani Exchange золотые тёмный циферблат</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Armani Exchange Classic — тёмный, золото&lt;br&gt;&lt;br&gt;Золотистый корпус и браслет, тёмный циферблат с тонкими золотыми метками — минимализм без лишних деталей. Ни даты, ни счётчиков: часы показывают время и не отвлекают. Универсальный вариант под костюм и под джинсы.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: сталь цвета золота&lt;br&gt;▫️ Циферблат: тёмный, золотые метки&lt;br&gt;▫️ Браслет: сталь цвета золота&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы armani exchange, armani золотые, часы мужские золото, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange Classic</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/wG-uwycLBbv6Tg</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_AX_chrono_all_blue_2</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nT3aFdg.jpg | https://iili.io/nT3aG49.jpg | https://iili.io/nT3at4t.jpg | https://iili.io/nT3cl9a.jpg | https://iili.io/nT3l7Wl.jpg | https://iili.io/nT30lQR.jpg</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Всё чёрное — Armani Exchange хронограф</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Armani Exchange Chronograph — чёрный, матовый корпус&lt;br&gt;&lt;br&gt;Матовый чёрный корпус, тёмный циферблат и силиконовый ремешок — монохром, который разбавляет только жёлтая секундная стрелка. Лёгкие, не цепляются за рукав, подходят и для города, и для спорта.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: матовый чёрный&lt;br&gt;▫️ Циферблат: чёрный, счётчик хронографа, жёлтая секундная стрелка, окно даты&lt;br&gt;▫️ Ремешок: чёрный силикон&lt;br&gt;▫️ Функции: хронограф, дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы armani exchange, armani хронограф чёрный, чёрные часы мужские, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Armani Exchange Chronograph</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Календарь | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Силикон</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/Ybh4p1xBQgWAwQ</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i3_Diesel_MegaChief_gold_green</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nT3GsZG.jpg | https://iili.io/nT3VFbn.jpg | https://iili.io/nT3jOZX.jpg | https://iili.io/nT3wRPs.jpg | https://iili.io/nT3Nfz7.jpg | https://iili.io/nT3NjLX.jpg</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный на золоте — Diesel Mega Chief</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Diesel Mega Chief — зелёный, золото&lt;br&gt;&lt;br&gt;Золотистый корпус-гигант и изумрудный циферблат — сочетание, которое не спутать ни с чем. Носят с худи и курткой, под тонкий рукав такие часы не прячут, да и незачем.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: цвет золота, крупный размер&lt;br&gt;▫️ Циферблат: зелёный, счётчики хронографа, окно даты&lt;br&gt;▫️ Браслет: цвет золота&lt;br&gt;▫️ Функции: хронограф, дата, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы diesel мужские, diesel mega chief, крупные часы золото, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14500</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diesel</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diesel Mega Chief</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Календарь | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Браслет</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/iNCA4mMPpOL6yQ</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K5:K1048576">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -19401,6 +19401,1376 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_orange</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuU3o2j.jpg | https://iili.io/nuU3Epp.jpg | https://iili.io/nuU3Q8x.jpg | https://iili.io/nuUF2cJ.jpg | https://iili.io/nuUF5Al.jpg | https://iili.io/nuUFMSj.jpg</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оранжевый огонь — Hublot Spirit скелетон</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — оранжевый, скелетон&lt;br&gt;&lt;br&gt;Бочкообразный корпус, открытый механизм и оранжевый каучук — часы, которые видно раньше, чем их владельца. Берут их не под костюм, а под футболку и кроссовки: там они работают как яркая деталь, ради которой к вам и подойдут с вопросом.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, оранжевый, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, три счётчика&lt;br&gt;▫️ Ремешок: каучук, оранжевый&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit of big bang, часы скелетон, наручные часы хронограф</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15900</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оранжевый</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/CAOCBL7EisuAMg</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_yellow</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUfYG9.jpg | https://iili.io/nuUf0Yb.jpg | https://iili.io/nuUfO3g.jpg | https://iili.io/nuUfDu4.jpg | https://iili.io/nuUqfAx.jpg | https://iili.io/nuUqgHb.jpg | https://iili.io/nuUBfgn.jpg | https://iili.io/nuUB1zQ.jpg | https://iili.io/nuUBrrX.jpg | https://iili.io/nuUBtQ2.jpg</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый неон — Hublot Spirit скелетон каучук</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — жёлтый, скелетон&lt;br&gt;&lt;br&gt;Кислотный жёлтый — самый заметный цвет в линейке. Такие часы не теряются на руке ни летом, ни под тёмным рукавом, а открытый механизм добавляет им дорогого вида вблизи, когда собеседник уже присмотрелся.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, жёлтый, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, три счётчика&lt;br&gt;▫️ Ремешок: каучук, жёлтый&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit жёлтый, яркие часы мужские, наручные часы скелетон</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15900</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/FSVpEQSox6h55A</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_lightblue</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUCEyG.jpg | https://iili.io/nuUCMuf.jpg | https://iili.io/nuUCWZl.jpg | https://iili.io/nuUCw67.jpg | https://iili.io/nuUCk8u.jpg | https://iili.io/nuUCvyb.jpg</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Голубая бочка — Hublot Spirit скелетон</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — голубой, скелетон&lt;br&gt;&lt;br&gt;Голубой мягче синего и заметно реже встречается. Хорошо ложится на загорелую руку и спокойно живёт с джинсой — вариант для тех, кто хочет цвет, но без крика.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, голубой, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, синие счётчики&lt;br&gt;▫️ Ремешок: каучук, голубой&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit голубой, часы скелетон каучук, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15900</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Голубой</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/hWjS6rA8T_HhnA</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_blue</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUnxPS.jpg | https://iili.io/nuUnRHu.jpg | https://iili.io/nuUncoQ.jpg | https://iili.io/nuUnMUF.jpg | https://iili.io/nuUnjDv.jpg | https://iili.io/nuUnvfI.jpg</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Hublot Spirit синий скелетон каучук</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — синий, скелетон&lt;br&gt;&lt;br&gt;Насыщенный синий — самый универсальный из ярких: сочетается и с джинсами, и с тёмным пиджаком. Открытый механизм видно и через циферблат, и через заднюю крышку.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, синий, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, синие счётчики&lt;br&gt;▫️ Ремешок: каучук, синий&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit синий, часы скелетон, наручные часы хронограф</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15900</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Синий</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/sI_xfD8PJRMvfA</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_carbon_red</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUoXr7.jpg | https://iili.io/nuUoOmb.jpg | https://iili.io/nuUo8LQ.jpg | https://iili.io/nuUoPYF.jpg | https://iili.io/nuUobBp.jpg | https://iili.io/nuUxHYX.jpg</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Карбон и красный — Hublot Spirit скелетон</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон чёрно-красный, скелетон&lt;br&gt;&lt;br&gt;Корпус под карбон с красными разводами — рисунок у каждого экземпляра свой, двух одинаковых не бывает. Красные счётчики на тёмном скелетоне дают тот самый гоночный вид, за который эту линейку и берут.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-красный&lt;br&gt;▫️ Циферблат: скелетон, красные счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон, часы скелетон красные, наручные часы хронограф</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16900</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit Carbon</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/MoS0UZgvxSuB-g</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_carbon_yellow</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUxjGp.jpg | https://iili.io/nuUxw6N.jpg | https://iili.io/nuUxeat.jpg | https://iili.io/nuUxUwG.jpg | https://iili.io/nuUxsFS.jpg | https://iili.io/nuUxQS9.jpg</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Карбон и жёлтый — Hublot Spirit скелетон</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон чёрно-жёлтый, скелетон&lt;br&gt;&lt;br&gt;Тёмный карбон с жёлтыми прожилками и жёлтые стрелки — сочетание, которое читается даже издалека, но не выглядит пластиковым. Лёгкий корпус почти не чувствуется на руке.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-жёлтый&lt;br&gt;▫️ Циферблат: скелетон, жёлтые стрелки и счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон жёлтый, часы скелетон, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16900</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Жёлтый</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit Carbon</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/Mo1EUnjoEmJ7Qg</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_carbon_green</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUzlV4.jpg | https://iili.io/nuUzWJ9.jpg | https://iili.io/nuUzjDb.jpg | https://iili.io/nuUzvfV.jpg | https://iili.io/nuUzr5F.jpg | https://iili.io/nuUzsWv.jpg</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Карбон и зелёный — Hublot Spirit скелетон</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон чёрно-зелёный, скелетон&lt;br&gt;&lt;br&gt;Зелёный по карбону — самая редкая расцветка линейки. На свету рисунок корпуса переливается, в тени часы выглядят почти чёрными: две разные вещи в одной.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-зелёный&lt;br&gt;▫️ Циферблат: скелетон, зелёные метки&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон зелёный, часы скелетон, наручные часы хронограф</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16900</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Зелёный</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit Carbon</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/eHpwgSru5lD_0Q</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_carbon_grey</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUIckF.jpg | https://iili.io/nuUIXrN.jpg | https://iili.io/nuUINkX.jpg | https://iili.io/nuUIUB4.jpg | https://iili.io/nuUIr42.jpg | https://iili.io/nuUIspe.jpg</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы Hublot Spirit карбон серый скелетон</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон серый, скелетон&lt;br&gt;&lt;br&gt;Серый карбон без цветных вставок — вариант для тех, кому нужен характер линейки, но не нужен цвет. Такие часы одинаково уместны и с толстовкой, и с пиджаком.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон серый&lt;br&gt;▫️ Циферблат: скелетон, светлые счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон, часы скелетон серые, наручные часы кварц</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16900</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Серый</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit Carbon</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/9zl4C0yF2bSSOg</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_Spirit_black_matte</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUTjMx.jpg | https://iili.io/nuUTOFV.jpg | https://iili.io/nuUTSAF.jpg | https://iili.io/nuUT6Mv.jpg | https://iili.io/nuUTQSI.jpg | https://iili.io/nuUTbNn.jpg</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный матовый — Hublot Spirit скелетон</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — чёрный матовый, скелетон&lt;br&gt;&lt;br&gt;Полностью чёрный корпус без блеска — самая спокойная версия линейки и самая ходовая. Скелетон читается только вблизи, поэтому часы одновременно и сдержанные, и с секретом.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, чёрный матовый&lt;br&gt;▫️ Циферблат: скелетон, светлые стрелки&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot чёрные, часы скелетон, наручные часы хронограф</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16400</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Чёрный</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/CDgH6picQ-ZMaw</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">i4_Hublot_BigBang_red_rubber</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Package</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79337583089</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Москва, Тверская улица</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://iili.io/nuUuizu.jpg | https://iili.io/nuUA9mF.jpg | https://iili.io/nuUAFqv.jpg | https://iili.io/nuUAnet.jpg | https://iili.io/nuUATLG.jpg | https://iili.io/nuUA5rl.jpg</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный каучук — часы Hublot Big Bang</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⌚ Hublot Big Bang — красный каучук, чёрный безель&lt;br&gt;&lt;br&gt;Круглый корпус Big Bang с чёрным безелем и цифрами по кругу, открытая механика в центре и красный каучук — классика бренда в самой узнаваемой подаче. Красный ремешок при желании меняется на чёрный за минуту.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: круглый, чёрный безель с цифрами&lt;br&gt;▫️ Циферблат: скелетон, красная стрелка&lt;br&gt;▫️ Ремешок: каучук, красный&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot big bang, часы скелетон красные, наручные часы</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы и украшения</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17900</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Часы</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Новое</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Красный</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hublot Big Bang Red</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные или карманные</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Наручные часы</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мужские</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кварцевые</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Водонепроницаемые</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Каучуковый</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://disk.yandex.ru/i/cqq1WxdWQ2eGnQ</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="K5:K1048576">
     <cfRule type="expression" priority="1" dxfId="0">

--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -2966,7 +2966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF115"/>
+  <dimension ref="A1:AF125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Tissot PRX Chronograph «Панда» — белый и синий 🔥&lt;/p&gt; &lt;p&gt;Белый циферблат с тремя синими субциферблатами — классическое сочетание, которое часовые фанаты называют «Панда». Чистый, читаемый и при этом по-настоящему стильный вид. Tissot PRX Chronograph — швейцарский хронограф с интегрированным браслетом, который выглядит значительно дороже своей цены.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: &lt;strong&gt;Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;🔖 &lt;strong&gt;РАСПРОДАЖА&lt;/strong&gt; до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите &lt;strong&gt;видео&lt;/strong&gt; до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло класса A+ с антибликовым покрытием&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и интегрированный браслет&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с синими субциферблатами «Панда»&lt;/p&gt; &lt;p&gt;✅ Хронограф — секунды, минуты, часы&lt;/p&gt; &lt;p&gt;✅ Дата на 4:30&lt;/p&gt; &lt;p&gt;✅ Водозащита 30 м&lt;/p&gt; &lt;p&gt;✅ Корпус 43 мм&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой: — внешний осмотр со всех сторон — проверка хода и точности — работа всего функционала (хронограф, дата)&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Tissot PRX Chronograph «Панда» — белый и синий 🔥&lt;/p&gt; &lt;p&gt;Белый циферблат с тремя синими субциферблатами — классическое сочетание, которое часовые фанаты называют «Панда». Чистый, читаемый и при этом по-настоящему стильный вид. Tissot PRX Chronograph, который выглядит значительно дороже своей цены.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: &lt;strong&gt;Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;🔖 &lt;strong&gt;РАСПРОДАЖА&lt;/strong&gt; до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите &lt;strong&gt;видео&lt;/strong&gt; до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло класса A+ с антибликовым покрытием&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и интегрированный браслет&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с синими субциферблатами «Панда»&lt;/p&gt; &lt;p&gt;✅ Хронограф — секунды, минуты, часы&lt;/p&gt; &lt;p&gt;✅ Дата на 4:30&lt;/p&gt; &lt;p&gt;✅ Водозащита 30 м&lt;/p&gt; &lt;p&gt;✅ Корпус 43 мм&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой: — внешний осмотр со всех сторон — проверка хода и точности — работа всего функционала (хронограф, дата)&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Bvlgari Serpenti Tubogas — змея Steel/Rose 🔥&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;Расцветка «сталь с розовым золотом» — один из самых узнаваемых символов ювелирного дома Bvlgari. Браслет-змея Tubogas дважды обвивает запястье: чередующиеся полосы стали и розового золота, яйцеобразный корпус с розово-золотым обрамлением, белый циферблат с римскими цифрами и рубиновая кабошон-корона. Это не просто часы — это украшение с характером.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: &lt;strong&gt;Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 &lt;strong&gt;РАСПРОДАЖА&lt;/strong&gt; до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите&lt;strong&gt; видео&lt;/strong&gt; до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Браслет-змея Tubogas — двойной виток, сталь + розовое золото&lt;/p&gt; &lt;p&gt;✅ Яйцеобразный корпус с розово-золотым обрамлением&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с римскими цифрами&lt;/p&gt; &lt;p&gt;✅ Розово-золотые индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Корона с рубиновым кабошоном&lt;/p&gt; &lt;p&gt;✅ Женские часы&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Bvlgari Serpenti Tubogas — змея Steel/Rose 🔥&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;Расцветка «сталь с розовым золотом» — один из самых узнаваемых символов ювелирного дома Bvlgari. Браслет-змея Tubogas дважды обвивает запястье: чередующиеся полосы стали и розового золота, яйцеобразный корпус с розово-золотым обрамлением, белый циферблат с римскими цифрами и рубиновая кабошон-корона. Это не просто часы — это украшение с характером.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: &lt;strong&gt;Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 &lt;strong&gt;РАСПРОДАЖА&lt;/strong&gt; до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите&lt;strong&gt; видео&lt;/strong&gt; до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Браслет-змея Tubogas — двойной виток, сталь + розовое золото&lt;/p&gt; &lt;p&gt;✅ Яйцеобразный корпус с розово-золотым обрамлением&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с римскими цифрами&lt;/p&gt; &lt;p&gt;✅ Розово-золотые индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Корона с рубиновым кабошоном&lt;/p&gt; &lt;p&gt;✅ Женские часы&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Зелёный Бонд — Seamaster изумруд, живая волна</t>
+          <t>Зелёный Бонд — Omega Seamaster изумруд</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — зелёная волна, сталь 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый горячий цвет года на дайверском корпусе&lt;/p&gt; &lt;p&gt;Расцветка «малахитовая волна» — глубокий изумрудно-зелёный циферблат с рельефной волной и зелёный керамический безель. Тональный зелёный от безеля до циферблата — именно так выглядит цвет, за которым охотятся. Когда AP, Rolex и Patek все разом выпускают зелёные версии — это уже не тренд, это классика. Seamaster в зелёном — редкость и удар по взгляду одновременно.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Зелёный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Зелёный циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — зелёная волна, сталь 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый горячий цвет года на дайверском корпусе&lt;/p&gt; &lt;p&gt;Расцветка «малахитовая волна» — глубокий изумрудно-зелёный циферблат с рельефной волной и зелёный керамический безель. Тональный зелёный от безеля до циферблата — именно так выглядит цвет, за которым охотятся. Когда AP, Rolex и Patek все разом выпускают зелёные версии — это уже не тренд, это классика. Seamaster в зелёном — редкость и удар по взгляду одновременно.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Зелёный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Зелёный циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Запрещённые на суше — яхтенные часы start/stop</t>
+          <t>Запрещённые на суше — Omega яхтенные часы</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — America's Cup Edition, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ЛИМИТИРОВАННАЯ ВЕРСИЯ — гоночные часы с парусной регаты&lt;/p&gt; &lt;p&gt;Расцветка «яхтсмен» — белый циферблат, синий безель с красными вставками, надпись START на безеле, красные арабские цифры и надпись «America's Cup» на циферблате. Эти часы — официальный хронометр Кубка Америки, самой престижной парусной регаты в мире. Носить их на суше — это уже заявление. Таких на Авито единицы, и они уходят быстро.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий безель с красными вставками и надписью START&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с красными арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Надпись «America's Cup» на циферблате&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — America's Cup Edition, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ЛИМИТИРОВАННАЯ ВЕРСИЯ — гоночные часы с парусной регаты&lt;/p&gt; &lt;p&gt;Расцветка «яхтсмен» — белый циферблат, синий безель с красными вставками, надпись START на безеле, красные арабские цифры и надпись «America's Cup» на циферблате. Эти часы — официальный хронометр Кубка Америки, самой престижной парусной регаты в мире. Носить их на суше — это уже заявление. Таких на Авито единицы, и они уходят быстро.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий безель с красными вставками и надписью START&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с красными арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Надпись «America's Cup» на циферблате&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Bvlgari Octo Finissimo — чёрный, сталь 🔥&lt;/p&gt; &lt;p&gt;Расцветка «чёрный стелс» — чёрный циферблат с арабскими цифрами на 12 и 6 и стальной integrated-браслет. Octo Finissimo — одна из самых тонких и архитектурно смелых моделей в мире: восьмиугольный корпус плавно перетекает в браслет, образуя единый скульптурный силуэт. Минимализм высшего уровня — без дополнительных функций, только время и форма.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный корпус — фирменный силуэт Octo&lt;/p&gt; &lt;p&gt;✅ Ультратонкий профиль&lt;/p&gt; &lt;p&gt;✅ Корпус 40 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Bvlgari Octo Finissimo — чёрный, сталь 🔥&lt;/p&gt; &lt;p&gt;Расцветка «чёрный стелс» — чёрный циферблат с арабскими цифрами на 12 и 6 и стальной integrated-браслет. Octo Finissimo — одна из самых тонких и архитектурно смелых моделей в мире: восьмиугольный корпус плавно перетекает в браслет, образуя единый скульптурный силуэт. Минимализм высшего уровня — без дополнительных функций, только время и форма.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный корпус — фирменный силуэт Octo&lt;/p&gt; &lt;p&gt;✅ Ультратонкий профиль&lt;/p&gt; &lt;p&gt;✅ Корпус 40 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Royal Oak серый — для тех, кто устал кричать</t>
+          <t>Royal Oak серый — Audemars Piguet, смелым</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak — серый таписсери, автомат 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — цвет для тех, кто не объясняет&lt;/p&gt; &lt;p&gt;Серый «гран-таписсери» — самый сдержанный и одновременно самый статусный вариант Royal Oak. Никакого крика, никакого синего или зелёного для привлечения внимания. Просто идеальная геометрия, идеальный фактурный узор, идеальный браслет. Те, кто разбираются — узнают сразу. Остальные просто чувствуют: что-то не так дёшево стоит. Редкий цвет, который сложнее всего найти в этом исполнении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: автоподзавод Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Серый фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak — серый таписсери, автомат 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — цвет для тех, кто не объясняет&lt;/p&gt; &lt;p&gt;Серый «гран-таписсери» — самый сдержанный и одновременно самый статусный вариант Royal Oak. Никакого крика, никакого синего или зелёного для привлечения внимания. Просто идеальная геометрия, идеальный фактурный узор, идеальный браслет. Те, кто разбираются — узнают сразу. Остальные просто чувствуют: что-то не так дёшево стоит. Редкий цвет, который сложнее всего найти в этом исполнении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Серый фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Royal Oak тёмный + розовое золото — бомба</t>
+          <t>Royal Oak+розовое золото — Audemars Piguet</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak — тёмно-синий + розовое золото, автомат 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — редкий биколор, которого мало у кого есть&lt;/p&gt; &lt;p&gt;Тёмно-синий «гран-таписсери» на корпусе из розового золота — это не просто часы, это заявление. Холодный синий против тёплого золота: такое сочетание носят только те, кто понимает. Royal Oak с 1972 года — часы, которые разрушили правила люксовой индустрии. Эта расцветка — самая редкая и желанная в линейке. Вас будут спрашивать, где взяли, каждый раз как наденете.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: автоподзавод Swiss Made&lt;/p&gt; &lt;p&gt;✅ Корпус и браслет — розовое золото + нержавеющая сталь 904L&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Тёмно-синий фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak — тёмно-синий + розовое золото, автомат 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — редкий биколор, которого мало у кого есть&lt;/p&gt; &lt;p&gt;Тёмно-синий «гран-таписсери» на корпусе из розового золота — это не просто часы, это заявление. Холодный синий против тёплого золота: такое сочетание носят только те, кто понимает. Royal Oak с 1972 года — часы, которые разрушили правила люксовой индустрии. Эта расцветка — самая редкая и желанная в линейке. Вас будут спрашивать, где взяли, каждый раз как наденете.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом&lt;/p&gt; &lt;p&gt;✅ Корпус и браслет — розовое золото + нержавеющая сталь 904L&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Тёмно-синий фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak Automatic — чёрный таписсери 🔥&lt;/p&gt; &lt;p&gt;Расцветка «чёрный гран-таписсери» — один из самых знаковых вариантов Royal Oak. Глубокий чёрный фактурный циферблат с люминесцентными индексами, восьмиугольный безель с восемью винтами и фирменный integrated-браслет. Дата на 3:00. Именно эту модель носят Drake, Jay-Z, LeBron James и другие иконы стиля. Культовые часы с 1972 года.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: автоподзавод Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (дата, автоподзавод)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak Automatic — чёрный таписсери 🔥&lt;/p&gt; &lt;p&gt;Расцветка «чёрный гран-таписсери» — один из самых знаковых вариантов Royal Oak. Глубокий чёрный фактурный циферблат с люминесцентными индексами, восьмиугольный безель с восемью винтами и фирменный integrated-браслет. Дата на 3:00. Именно эту модель носят Drake, Jay-Z, LeBron James и другие иконы стиля. Культовые часы с 1972 года.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (дата, автоподзавод)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Убийца всех дайверов — 600 метров, полный чёрный</t>
+          <t>Убийца дайверов — Omega 600м, полный чёрный</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — полный чёрный, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый серьёзный дайвер на рынке&lt;/p&gt; &lt;p&gt;Расцветка «стелс» — полностью чёрный безель, чёрный циферблат и стальной браслет. Никакого цвета, никаких лишних деталей. Planet Ocean — это уже не про красоту, это про характер. Водозащита 600 метров, керамический безель ZrO₂, корпус 45 мм. Мощь без слов. Рядом с этим большинство часов на запястьях выглядят игрушками.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель ZrO₂&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с люминесцентными индексами&lt;/p&gt; &lt;p&gt;✅ Арабские цифры 12 и 9&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — полный чёрный, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый серьёзный дайвер на рынке&lt;/p&gt; &lt;p&gt;Расцветка «стелс» — полностью чёрный безель, чёрный циферблат и стальной браслет. Никакого цвета, никаких лишних деталей. Planet Ocean — это уже не про красоту, это про характер. Водозащита 600 метров, керамический безель ZrO₂, корпус 45 мм. Мощь без слов. Рядом с этим большинство часов на запястьях выглядят игрушками.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель ZrO₂&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с люминесцентными индексами&lt;/p&gt; &lt;p&gt;✅ Арабские цифры 12 и 9&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak Automatic — зелёный таписсери 🔥&lt;/p&gt; &lt;p&gt;Расцветка «зелёный гран-таписсери» — один из самых желанных вариантов Royal Oak последних лет. Насыщенный изумрудно-зелёный фактурный циферблат, восьмиугольный безель с восемью винтами и фирменный integrated-браслет из нержавеющей стали. Именно в этом цвете AP выпустил лимитированную серию к 50-летию Royal Oak — и он мгновенно стал легендарным.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: автоподзавод Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Зелёный фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (дата, автоподзавод)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak Automatic — зелёный таписсери 🔥&lt;/p&gt; &lt;p&gt;Расцветка «зелёный гран-таписсери» — один из самых желанных вариантов Royal Oak последних лет. Насыщенный изумрудно-зелёный фактурный циферблат, восьмиугольный безель с восемью винтами и фирменный integrated-браслет из нержавеющей стали. Именно в этом цвете AP выпустил лимитированную серию к 50-летию Royal Oak — и он мгновенно стал легендарным.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Зелёный фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (дата, автоподзавод)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Убийца дресс-кода — Royal Oak синий, автомат</t>
+          <t>Убийца дресс-кода — Audemars Piguet синий</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak — синий таписсери, автомат 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самые узнаваемые часы в мире&lt;/p&gt; &lt;p&gt;Эти часы перевернули индустрию в 1972 году — когда стальные часы за такие деньги считались безумием. Сегодня Royal Oak носят Drake, LeBron James, Jay-Z и половина Forbes. Синий «гран-таписсери» — фактурный узор, который виден за три метра. Один взгляд на запястье — и всё понятно без слов. Аналогов по деталировке и внешнему виду на этом ценовом уровне просто нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: автоподзавод Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — именно поэтому часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Audemars Piguet Royal Oak — синий таписсери, автомат 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самые узнаваемые часы в мире&lt;/p&gt; &lt;p&gt;Эти часы перевернули индустрию в 1972 году — когда стальные часы за такие деньги считались безумием. Сегодня Royal Oak носят Drake, LeBron James, Jay-Z и половина Forbes. Синий «гран-таписсери» — фактурный узор, который виден за три метра. Один взгляд на запястье — и всё понятно без слов. Аналогов по деталировке и внешнему виду на этом ценовом уровне просто нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий фактурный циферблат «гран-таписсери»&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный безель с 8 гексагональными винтами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — именно поэтому часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Bvlgari Octo Finissimo — арабские цифры, белый, сталь 🔥&lt;/p&gt; &lt;p&gt;Расцветка «белый с арабской вязью» — молочно-белый циферблат с цифрами на арабском языке и стальной integrated-браслет. Редкая специальная версия Octo для ближневосточного рынка в стальном корпусе: светлая и элегантная альтернатива тёмной DLC-версии. Восьмиугольный корпус, ультратонкий профиль, никаких лишних деталей — только форма и шрифт.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный корпус — фирменный силуэт Octo&lt;/p&gt; &lt;p&gt;✅ Ультратонкий профиль&lt;/p&gt; &lt;p&gt;✅ Корпус 40 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Bvlgari Octo Finissimo — арабские цифры, белый, сталь 🔥&lt;/p&gt; &lt;p&gt;Расцветка «белый с арабской вязью» — молочно-белый циферблат с цифрами на арабском языке и стальной integrated-браслет. Редкая специальная версия Octo для ближневосточного рынка в стальном корпусе: светлая и элегантная альтернатива тёмной DLC-версии. Восьмиугольный корпус, ультратонкий профиль, никаких лишних деталей — только форма и шрифт.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный корпус — фирменный силуэт Octo&lt;/p&gt; &lt;p&gt;✅ Ультратонкий профиль&lt;/p&gt; &lt;p&gt;✅ Корпус 40 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — чёрный + оранжевый, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый мощный дайвер от Omega&lt;/p&gt; &lt;p&gt;Расцветка «закат» — чёрный безель с оранжевой вставкой в верхней части и оранжевые арабские цифры на циферблате. Planet Ocean — это старший брат Seamaster: глубина 600 м, корпус 45 мм, массивный и агрессивный. Именно эту модель выбирают те, кому обычный Seamaster кажется слишком тихим. Носить такое — значит знать, что делаешь.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный безель с оранжевой вставкой&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с оранжевыми арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — чёрный + оранжевый, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый мощный дайвер от Omega&lt;/p&gt; &lt;p&gt;Расцветка «закат» — чёрный безель с оранжевой вставкой в верхней части и оранжевые арабские цифры на циферблате. Planet Ocean — это старший брат Seamaster: глубина 600 м, корпус 45 мм, массивный и агрессивный. Именно эту модель выбирают те, кому обычный Seamaster кажется слишком тихим. Носить такое — значит знать, что делаешь.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный безель с оранжевой вставкой&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с оранжевыми арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Invicta Reserve — золотая цепь + чёрный, хронограф 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — часы как у рэпера, серьёзно&lt;/p&gt; &lt;p&gt;Расцветка «чёрное золото» — полностью чёрный корпус и циферблат, массивная плетёная золотая цепь вместо браслета, золотые акценты на субциферблате. Это Invicta Reserve в версии «без тормозов». Именно такое носят на треке и на яхте одновременно. Corпус 55 мм, зубчатый безель, день недели, дата, хронограф — и золотая цепь, которую заметно с другого конца улицы. Часы для тех, кто привык быть главным в любой комнате.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф Swiss Movement&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — чёрный DLC-корпус&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный зубчатый безель&lt;/p&gt; &lt;p&gt;✅ Чёрный многоуровневый циферблат&lt;/p&gt; &lt;p&gt;✅ Хронограф — 3 субциферблата&lt;/p&gt; &lt;p&gt;✅ День недели + дата&lt;/p&gt; &lt;p&gt;✅ Массивная плетёная золотая цепь — браслет&lt;/p&gt; &lt;p&gt;✅ Корпус 55 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (хронограф, дата, день недели)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле — Rolex,  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Invicta Reserve — золотая цепь + чёрный, хронограф 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — часы как у рэпера, серьёзно&lt;/p&gt; &lt;p&gt;Расцветка «чёрное золото» — полностью чёрный корпус и циферблат, массивная плетёная золотая цепь вместо браслета, золотые акценты на субциферблате. Это Invicta Reserve в версии «без тормозов». Именно такое носят на треке и на яхте одновременно. Corпус 55 мм, зубчатый безель, день недели, дата, хронограф — и золотая цепь, которую заметно с другого конца улицы. Часы для тех, кто привык быть главным в любой комнате.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — чёрный DLC-корпус&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный зубчатый безель&lt;/p&gt; &lt;p&gt;✅ Чёрный многоуровневый циферблат&lt;/p&gt; &lt;p&gt;✅ Хронограф — 3 субциферблата&lt;/p&gt; &lt;p&gt;✅ День недели + дата&lt;/p&gt; &lt;p&gt;✅ Массивная плетёная золотая цепь — браслет&lt;/p&gt; &lt;p&gt;✅ Корпус 55 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (хронограф, дата, день недели)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле — Rolex,  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Синяя легенда-Seamaster синяя волна,оригинал Бонда</t>
+          <t>Синяя легенда — Omega Seamaster Бонда</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — синяя волна, классика 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый узнаваемый дайвер в истории кино&lt;/p&gt; &lt;p&gt;Расцветка «глубокий синий» — синий волнообразный циферблат и синий керамический безель. Это та самая, каноническая расцветка Seamaster, в которой Дэниел Крейг выходил из воды в «Казино Рояль». Тональный синий от безеля до циферблата, красная секундная стрелка — единственный яркий штрих. Часы, которые знают все. Просить объяснений не придётся — объяснять будете вы.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Синий циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Красная секундная стрелка&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — синяя волна, классика 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самый узнаваемый дайвер в истории кино&lt;/p&gt; &lt;p&gt;Расцветка «глубокий синий» — синий волнообразный циферблат и синий керамический безель. Это та самая, каноническая расцветка Seamaster, в которой Дэниел Крейг выходил из воды в «Казино Рояль». Тональный синий от безеля до циферблата, красная секундная стрелка — единственный яркий штрих. Часы, которые знают все. Просить объяснений не придётся — объяснять будете вы.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Синий циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Красная секундная стрелка&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Лава встречает океан —Planet Ocean серый+оранжевый</t>
+          <t>Лава и океан — Omega Planet Ocean, оранж</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — серый + оранжевый, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — редчайший биколор, который останавливает взгляд&lt;/p&gt; &lt;p&gt;Расцветка «раскалённая лава» — тёмно-серый циферблат, чёрный безель с огненно-оранжевой вставкой и оранжевые арабские цифры. Это не просто часы — это характер. Именно так выглядит Planet Ocean Deep Black в версии, которую делали для любителей экстрима. Тёмный и агрессивный сверху, взрывной оранжевый снизу. Аналогов по сочетанию цветов на Авито попросту нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный безель с оранжевой вставкой в нижней части&lt;/p&gt; &lt;p&gt;✅ Тёмно-серый циферблат с оранжевыми арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — серый + оранжевый, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — редчайший биколор, который останавливает взгляд&lt;/p&gt; &lt;p&gt;Расцветка «раскалённая лава» — тёмно-серый циферблат, чёрный безель с огненно-оранжевой вставкой и оранжевые арабские цифры. Это не просто часы — это характер. Именно так выглядит Planet Ocean Deep Black в версии, которую делали для любителей экстрима. Тёмный и агрессивный сверху, взрывной оранжевый снизу. Аналогов по сочетанию цветов на Авито попросту нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный безель с оранжевой вставкой в нижней части&lt;/p&gt; &lt;p&gt;✅ Тёмно-серый циферблат с оранжевыми арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Люминесцентные индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Seamaster 007 Edition — скрытый узор на циферблате</t>
+          <t>Omega Seamaster 007 — узор на циферблате</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Professional — James Bond Edition, 007-узор 🔥&lt;/p&gt; &lt;p&gt;🔥 ЛИМИТИРОВАННАЯ ВЕРСИЯ — циферблат с секретом&lt;/p&gt; &lt;p&gt;Присмотритесь к циферблату: по всей поверхности скрытый повторяющийся узор «007». Это лимитированная версия Seamaster, выпущенная специально к франшизе Джеймса Бонда. Обычный Seamaster уже культовый. Этот — разговор на другом уровне. Если кто-то заметит узор — он свой. Таких на Авито единицы. Носить и молчать, пока не спросят.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат со скрытым узором «007» по всей поверхности&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Красная секундная стрелка&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Professional — James Bond Edition, 007-узор 🔥&lt;/p&gt; &lt;p&gt;🔥 ЛИМИТИРОВАННАЯ ВЕРСИЯ — циферблат с секретом&lt;/p&gt; &lt;p&gt;Присмотритесь к циферблату: по всей поверхности скрытый повторяющийся узор «007». Это лимитированная версия Seamaster, выпущенная специально к франшизе Джеймса Бонда. Обычный Seamaster уже культовый. Этот — разговор на другом уровне. Если кто-то заметит узор — он свой. Таких на Авито единицы. Носить и молчать, пока не спросят.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат со скрытым узором «007» по всей поверхности&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Красная секундная стрелка&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Bvlgari Serpenti Tubogas — змея с бриллиантами 🔥&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;Расцветка «сталь с жёлтым золотом» — и главное отличие этой версии: корпус полностью окантован сверкающими камнями. Браслет-змея Tubogas дважды обвивает запястье, чередуя стальные и жёлто-золотые полосы. Белый циферблат с римскими цифрами, золотые стрелки и рубиновая корона-кабошон. Максимально нарядная версия Serpenti — для тех, кто не хочет идти на компромисс.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: &lt;strong&gt;Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 &lt;strong&gt;РАСПРОДАЖА&lt;/strong&gt; до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите &lt;strong&gt;видео &lt;/strong&gt;до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Swiss Made&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Браслет-змея Tubogas — двойной виток, сталь + жёлтое золото&lt;/p&gt; &lt;p&gt;✅ Яйцеобразный корпус в жёлто-золотом обрамлении&lt;/p&gt; &lt;p&gt;✅ Обводка корпуса из сверкающих камней&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с римскими цифрами&lt;/p&gt; &lt;p&gt;✅ Золотые индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Корона с рубиновым кабошоном&lt;/p&gt; &lt;p&gt;✅ Женские часы&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Bvlgari Serpenti Tubogas — змея с бриллиантами 🔥&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;Расцветка «сталь с жёлтым золотом» — и главное отличие этой версии: корпус полностью окантован сверкающими камнями. Браслет-змея Tubogas дважды обвивает запястье, чередуя стальные и жёлто-золотые полосы. Белый циферблат с римскими цифрами, золотые стрелки и рубиновая корона-кабошон. Максимально нарядная версия Serpenti — для тех, кто не хочет идти на компромисс.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: &lt;strong&gt;Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 &lt;strong&gt;РАСПРОДАЖА&lt;/strong&gt; до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите &lt;strong&gt;видео &lt;/strong&gt;до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Браслет-змея Tubogas — двойной виток, сталь + жёлтое золото&lt;/p&gt; &lt;p&gt;✅ Яйцеобразный корпус в жёлто-золотом обрамлении&lt;/p&gt; &lt;p&gt;✅ Обводка корпуса из сверкающих камней&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с римскими цифрами&lt;/p&gt; &lt;p&gt;✅ Золотые индексы и стрелки&lt;/p&gt; &lt;p&gt;✅ Корона с рубиновым кабошоном&lt;/p&gt; &lt;p&gt;✅ Женские часы&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -9910,12 +9910,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Белый Бонд — Seamaster белая волна + синий</t>
+          <t>Белый Бонд — Omega Seamaster белая волна</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — белая волна + синий безель 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — белый Seamaster, которого все ищут и мало кто находит&lt;/p&gt; &lt;p&gt;Расцветка «арктическая волна» — белоснежный циферблат с рельефной волной и синий керамический безель. Это самый редкий и самый обсуждаемый вариант Seamaster последних лет. Пока все носят чёрный — ты надеваешь белый. Волнообразный рельеф виден под углом, синие стрелки дают контраст. Элегантный, чистый и при этом дайверский характер. Аналогов по эффекту на запястье нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Синие стрелки с люминесцентным покрытием&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — белая волна + синий безель 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — белый Seamaster, которого все ищут и мало кто находит&lt;/p&gt; &lt;p&gt;Расцветка «арктическая волна» — белоснежный циферблат с рельефной волной и синий керамический безель. Это самый редкий и самый обсуждаемый вариант Seamaster последних лет. Пока все носят чёрный — ты надеваешь белый. Волнообразный рельеф виден под углом, синие стрелки дают контраст. Элегантный, чистый и при этом дайверский характер. Аналогов по эффекту на запястье нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Синие стрелки с люминесцентным покрытием&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
@@ -10640,12 +10640,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Seamaster Diver — серая волна + синий безель</t>
+          <t>Omega Seamaster Diver — серая волна, синий</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — серый волнообразный + синий безель 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — редкий биколор Seamaster&lt;/p&gt; &lt;p&gt;Расцветка «шторм» — серый волнообразный циферблат и ярко-синий керамический безель. Это один из самых нетривиальных вариантов Seamaster: не чёрный и не синий, а точно между. Серая «волна» на циферблате — фирменный узор Diver, который виден только под определённым углом. Сдержанно и дорого. Тех, кто знает — зацепит сразу.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Серый циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Синие стрелки с люминесцентным покрытием&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — серый волнообразный + синий безель 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — редкий биколор Seamaster&lt;/p&gt; &lt;p&gt;Расцветка «шторм» — серый волнообразный циферблат и ярко-синий керамический безель. Это один из самых нетривиальных вариантов Seamaster: не чёрный и не синий, а точно между. Серая «волна» на циферблате — фирменный узор Diver, который виден только под определённым углом. Сдержанно и дорого. Тех, кто знает — зацепит сразу.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Серый циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Синие стрелки с люминесцентным покрытием&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Бонд в белом — Seamaster белая волна + чёрный</t>
+          <t>Бонд в белом — Omega Seamaster, чёрный</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — белая волна + чёрный безель 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — контраст, который убивает взгляд&lt;/p&gt; &lt;p&gt;Расцветка «белый иней» — белоснежный волнообразный циферблат и чёрный керамический безель. Максимальный контраст: тёмный сверху, ослепительно белый внутри. Именно этот вариант считается самым дерзким в линейке Seamaster — белый циферблат на дайверском корпусе ломает все шаблоны. Пока все ходят в чёрном — ты выходишь в белом. Смотрят все. Спрашивают все.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Чёрные стрелки с люминесцентным покрытием&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Diver 300M — белая волна + чёрный безель 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — контраст, который убивает взгляд&lt;/p&gt; &lt;p&gt;Расцветка «белый иней» — белоснежный волнообразный циферблат и чёрный керамический безель. Максимальный контраст: тёмный сверху, ослепительно белый внутри. Именно этот вариант считается самым дерзким в линейке Seamaster — белый циферблат на дайверском корпусе ломает все шаблоны. Пока все ходят в чёрном — ты выходишь в белом. Смотрят все. Спрашивают все.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с волнообразным рельефом&lt;/p&gt; &lt;p&gt;✅ Чёрные стрелки с люминесцентным покрытием&lt;/p&gt; &lt;p&gt;✅ Дата на 6:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -11522,12 +11522,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Поглотитель взглядов — Planet Ocean синий, 600м</t>
+          <t>Поглотитель взглядов — Omega Planet Ocean</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — полный синий, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — тональный синий, который топит всё вокруг&lt;/p&gt; &lt;p&gt;Расцветка «глубокий океан» — синий циферблат, синий керамический безель, синие стрелки. Полностью тональный образ: надеваешь — и всё остальное на запястьях рядом выглядит как пластик. Planet Ocean — старший, самый мощный Seamaster. 600 метров глубины, корпус 45 мм, характер как у ледокола. Вас будут спрашивать, сколько стоит — каждый раз.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель&lt;/p&gt; &lt;p&gt;✅ Синий циферблат с люминесцентными индексами&lt;/p&gt; &lt;p&gt;✅ Синие стрелки&lt;/p&gt; &lt;p&gt;✅ Арабские цифры 12 и 9&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Planet Ocean — полный синий, 600 м 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — тональный синий, который топит всё вокруг&lt;/p&gt; &lt;p&gt;Расцветка «глубокий океан» — синий циферблат, синий керамический безель, синие стрелки. Полностью тональный образ: надеваешь — и всё остальное на запястьях рядом выглядит как пластик. Planet Ocean — старший, самый мощный Seamaster. 600 метров глубины, корпус 45 мм, характер как у ледокола. Вас будут спрашивать, сколько стоит — каждый раз.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Master Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий керамический безель&lt;/p&gt; &lt;p&gt;✅ Синий циферблат с люминесцентными индексами&lt;/p&gt; &lt;p&gt;✅ Синие стрелки&lt;/p&gt; &lt;p&gt;✅ Арабские цифры 12 и 9&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 600 м / 2000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 45 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Invicta Reserve Bolt — синий + жёлтое золото, хронограф 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — часы, которые не пройдут незамеченными&lt;/p&gt; &lt;p&gt;Расцветка «синяя сталь с золотом» — массивный корпус 52 мм с золотыми «когтями» по периметру безеля, синий безель с рифлёными кнопками и синий многоуровневый циферблат. Invicta Reserve Bolt — это не просто часы, это скульптура на запястье. Носят те, кому мало просто хорошего — нужно запредельное. День недели, дата, хронограф — и всё это в одном корпусе, который невозможно не заметить с трёх метров.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф Swiss Movement&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и браслет биколор&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий безель с золотыми «когтями» по периметру&lt;/p&gt; &lt;p&gt;✅ Синий многоуровневый циферблат&lt;/p&gt; &lt;p&gt;✅ Хронограф — 3 субциферблата&lt;/p&gt; &lt;p&gt;✅ День недели + дата&lt;/p&gt; &lt;p&gt;✅ Рифлёные кнопки и заводная головка&lt;/p&gt; &lt;p&gt;✅ Корпус 52 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (хронограф, дата, день недели)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Invicta Reserve Bolt — синий + жёлтое золото, хронограф 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — часы, которые не пройдут незамеченными&lt;/p&gt; &lt;p&gt;Расцветка «синяя сталь с золотом» — массивный корпус 52 мм с золотыми «когтями» по периметру безеля, синий безель с рифлёными кнопками и синий многоуровневый циферблат. Invicta Reserve Bolt — это не просто часы, это скульптура на запястье. Носят те, кому мало просто хорошего — нужно запредельное. День недели, дата, хронограф — и всё это в одном корпусе, который невозможно не заметить с трёх метров.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и браслет биколор&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Синий безель с золотыми «когтями» по периметру&lt;/p&gt; &lt;p&gt;✅ Синий многоуровневый циферблат&lt;/p&gt; &lt;p&gt;✅ Хронограф — 3 субциферблата&lt;/p&gt; &lt;p&gt;✅ День недели + дата&lt;/p&gt; &lt;p&gt;✅ Рифлёные кнопки и заводная головка&lt;/p&gt; &lt;p&gt;✅ Корпус 52 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (хронограф, дата, день недели)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Omega Seamaster Professional — чёрный, Co-Axial, сталь 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — часы агента 007 на вашем запястье&lt;/p&gt; &lt;p&gt;С 1995 года Omega Seamaster — официальные часы Джеймса Бонда. Чёрный керамический безель, чёрный циферблат с люминесцентными индексами и профессиональная водозащита 300 м. Именно эту модель Пирс Броснан, Дэниел Крейг и Роджер Мур надевали перед прыжком в воду. Брутально, функционально, узнаваемо — аналогов по харизме нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с люминесцентными индексами&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Omega Seamaster Professional — чёрный, Co-Axial, сталь 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — часы агента 007 на вашем запястье&lt;/p&gt; &lt;p&gt;С 1995 года Omega Seamaster — официальные часы Джеймса Бонда. Чёрный керамический безель, чёрный циферблат с люминесцентными индексами и профессиональная водозащита 300 м. Именно эту модель Пирс Броснан, Дэниел Крейг и Роджер Мур надевали перед прыжком в воду. Брутально, функционально, узнаваемо — аналогов по харизме нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: механический с автоподзаводом Co-Axial Chronometer&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь 904L — корпус и браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Чёрный керамический безель с минутной шкалой&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с люминесцентными индексами&lt;/p&gt; &lt;p&gt;✅ Дата на 3:00&lt;/p&gt; &lt;p&gt;✅ Водозащита 300 м / 1000 ft&lt;/p&gt; &lt;p&gt;✅ Корпус 41 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Tissot PRX Chronograph — синий циферблат, стиль 🔥&lt;/p&gt; &lt;p&gt;Глубокий синий циферблат с белыми субциферблатами хронографа — элегантное и при этом спортивное сочетание. Tissot PRX Chronograph давно стал символом доступного швейцарского премиума: интегрированный браслет, чёткие грани корпуса и безупречная сборка. Подходит и под деловой стиль, и под повседневный образ.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — &lt;strong&gt;вышлем промокод 5% на любые часы из профиля!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите &lt;strong&gt;видео&lt;/strong&gt; до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло класса A+ с антибликовым покрытием&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и интегрированный браслет&lt;/p&gt; &lt;p&gt;✅ Синий циферблат с белыми субциферблатами&lt;/p&gt; &lt;p&gt;✅ Хронограф — секунды, минуты, часы&lt;/p&gt; &lt;p&gt;✅ Дата на 4:30&lt;/p&gt; &lt;p&gt;✅ Водозащита 30 м&lt;/p&gt; &lt;p&gt;✅ Корпус 43 мм&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой: — внешний осмотр со всех сторон — проверка хода и точности — работа всего функционала (хронограф, дата)&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Tissot PRX Chronograph — синий циферблат, стиль 🔥&lt;/p&gt; &lt;p&gt;Глубокий синий циферблат с белыми субциферблатами хронографа — элегантное и при этом спортивное сочетание. Tissot PRX Chronograph давно стал символом доступного премиума: интегрированный браслет, чёткие грани корпуса и безупречная сборка. Подходит и под деловой стиль, и под повседневный образ.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — &lt;strong&gt;вышлем промокод 5% на любые часы из профиля!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите &lt;strong&gt;видео&lt;/strong&gt; до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло класса A+ с антибликовым покрытием&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и интегрированный браслет&lt;/p&gt; &lt;p&gt;✅ Синий циферблат с белыми субциферблатами&lt;/p&gt; &lt;p&gt;✅ Хронограф — секунды, минуты, часы&lt;/p&gt; &lt;p&gt;✅ Дата на 4:30&lt;/p&gt; &lt;p&gt;✅ Водозащита 30 м&lt;/p&gt; &lt;p&gt;✅ Корпус 43 мм&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой: — внешний осмотр со всех сторон — проверка хода и точности — работа всего функционала (хронограф, дата)&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Tissot PRX Chronograph — стильный хронограф 🔥&lt;/p&gt; &lt;p&gt;Tissot PRX — один из самых горячих хитов последних лет в мире доступной швейцарской классики. Интегрированный браслет, чёткие грани корпуса и лаконичный чёрный циферблат с тремя субциферблатами хронографа — всё это делает PRX Chronograph безупречным выбором для тех, кто ценит стиль без лишнего шума.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;&lt;strong&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло класса A+ с антибликовым покрытием&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и интегрированный браслет&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с тремя субциферблатами&lt;/p&gt; &lt;p&gt;✅ Хронограф — секунды, минуты, часы&lt;/p&gt; &lt;p&gt;✅ Дата на 4:30&lt;/p&gt; &lt;p&gt;✅ Водозащита 30 м&lt;/p&gt; &lt;p&gt;✅ Корпус 43 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой: — внешний осмотр со всех сторон — проверка хода и точности — работа всего функционала (хронограф, дата)&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Tissot PRX Chronograph — стильный хронограф 🔥&lt;/p&gt; &lt;p&gt;Tissot PRX — один из самых горячих хитов последних лет в мире доступной классики. Интегрированный браслет, чёткие грани корпуса и лаконичный чёрный циферблат с тремя субциферблатами хронографа — всё это делает PRX Chronograph безупречным выбором для тех, кто ценит стиль без лишнего шума.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;&lt;strong&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/strong&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло класса A+ с антибликовым покрытием&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус и интегрированный браслет&lt;/p&gt; &lt;p&gt;✅ Чёрный циферблат с тремя субциферблатами&lt;/p&gt; &lt;p&gt;✅ Хронограф — секунды, минуты, часы&lt;/p&gt; &lt;p&gt;✅ Дата на 4:30&lt;/p&gt; &lt;p&gt;✅ Водозащита 30 м&lt;/p&gt; &lt;p&gt;✅ Корпус 43 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой: — внешний осмотр со всех сторон — проверка хода и точности — работа всего функционала (хронограф, дата)&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Унисекс</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Bvlgari Octo Finissimo — арабские цифры, чёрный DLC 🔥&lt;/p&gt; &lt;p&gt;Расцветка «чёрный с кремовым» в арабской версии — кремово-белый циферблат с цифрами на арабском языке и чёрный DLC-корпус с integrated-браслетом. Ограниченная версия Octo, выпущенная специально для ближневосточного рынка и ставшая редкостью во всём мире. Один из самых необычных и разговорных циферблатов в современном люксе.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Swiss Made&lt;/p&gt; &lt;p&gt;✅ Чёрный DLC-корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Кремово-белый циферблат с арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный корпус — фирменный силуэт Octo&lt;/p&gt; &lt;p&gt;✅ Ультратонкий профиль&lt;/p&gt; &lt;p&gt;✅ Корпус 40 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Bvlgari Octo Finissimo — арабские цифры, чёрный DLC 🔥&lt;/p&gt; &lt;p&gt;Расцветка «чёрный с кремовым» в арабской версии — кремово-белый циферблат с цифрами на арабском языке и чёрный DLC-корпус с integrated-браслетом. Ограниченная версия Octo, выпущенная специально для ближневосточного рынка и ставшая редкостью во всём мире. Один из самых необычных и разговорных циферблатов в современном люксе.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый&lt;/p&gt; &lt;p&gt;✅ Чёрный DLC-корпус и integrated-браслет&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Кремово-белый циферблат с арабскими цифрами&lt;/p&gt; &lt;p&gt;✅ Восьмиугольный корпус — фирменный силуэт Octo&lt;/p&gt; &lt;p&gt;✅ Ультратонкий профиль&lt;/p&gt; &lt;p&gt;✅ Корпус 40 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Invicta Reserve — цепной браслет + синий космос, хронограф 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самые безумные часы, которые вы видели&lt;/p&gt; &lt;p&gt;Расцветка «тёмный космос» — синий многоуровневый циферблат со сложным геометрическим узором, стальной зубчатый безель и массивный плетёный цепной браслет в чёрном цвете. Это не часы — это заявление о том, кто ты. Invicta Reserve с цепным браслетом — вещь, которую надевают один раз и больше не снимают. Снял — потерял ощущение. Аналогов по дерзости на Авито нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф Swiss Movement&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Зубчатый стальной безель&lt;/p&gt; &lt;p&gt;✅ Синий многоуровневый циферблат с геометрическим узором&lt;/p&gt; &lt;p&gt;✅ Хронограф — 3 субциферблата&lt;/p&gt; &lt;p&gt;✅ День недели + дата&lt;/p&gt; &lt;p&gt;✅ Массивный плетёный цепной браслет — чёрный&lt;/p&gt; &lt;p&gt;✅ Корпус 55 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (хронограф, дата, день недели)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Invicta Reserve — цепной браслет + синий космос, хронограф 🔥&lt;/p&gt; &lt;p&gt;🔥 ХИТ ПРОДАЖ 2025–2026 — самые безумные часы, которые вы видели&lt;/p&gt; &lt;p&gt;Расцветка «тёмный космос» — синий многоуровневый циферблат со сложным геометрическим узором, стальной зубчатый безель и массивный плетёный цепной браслет в чёрном цвете. Это не часы — это заявление о том, кто ты. Invicta Reserve с цепным браслетом — вещь, которую надевают один раз и больше не снимают. Снял — потерял ощущение. Аналогов по дерзости на Авито нет.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый хронограф&lt;/p&gt; &lt;p&gt;✅ Нержавеющая сталь — корпус&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Зубчатый стальной безель&lt;/p&gt; &lt;p&gt;✅ Синий многоуровневый циферблат с геометрическим узором&lt;/p&gt; &lt;p&gt;✅ Хронограф — 3 субциферблата&lt;/p&gt; &lt;p&gt;✅ День недели + дата&lt;/p&gt; &lt;p&gt;✅ Массивный плетёный цепной браслет — чёрный&lt;/p&gt; &lt;p&gt;✅ Корпус 55 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Видео в объявлении — снято именно с этих часов. Что видите, то и получите. Никаких подмен и сюрпризов при получении.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала (хронограф, дата, день недели)&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ 90% продавцов на Авито отправляют без проверки — часы приезжают с браком или вообще не теми. Мы проверяем всё заранее — это наш стандарт, а не исключение.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле —  и другие. Кварцевые и механические, мужские и женские. Часы для кино, фильмов и сериалов. Опт и дроп — пишите. Есть вопросы? Пишите — отвечаю сразу. Добавьте в избранное, чтобы не потерять! &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>&lt;p&gt;⌚ Rolex 1908 — белый циферблат, жёлтое золото 🔥&lt;/p&gt; &lt;p&gt;Расцветка «белый с жёлтым золотом» — Rolex 1908 в золотом исполнении с белым лаконичным циферблатом, арабскими цифрами и субциферблатом малых секунд на 6:00. Модель 1908 — возвращение Rolex к своим истокам: выпущена в 2023 году как дань уважения самым первым часам марки. Золотой флютированный безель, золотой браслет Jubilee и чистейший белый циферблат — элегантность вне времени.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый Swiss Made&lt;/p&gt; &lt;p&gt;✅ Корпус и браслет Jubilee в цвете жёлтого золота&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с арабскими цифрами и золотыми индексами&lt;/p&gt; &lt;p&gt;✅ Флютированный безель&lt;/p&gt; &lt;p&gt;✅ Субциферблат малых секунд на 6:00&lt;/p&gt; &lt;p&gt;✅ Корпус 39 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле большой выбор:  и другие. Кварцевые &lt;/p&gt;</t>
+          <t>&lt;p&gt;⌚ Rolex 1908 — белый циферблат, жёлтое золото 🔥&lt;/p&gt; &lt;p&gt;Расцветка «белый с жёлтым золотом» — Rolex 1908 в золотом исполнении с белым лаконичным циферблатом, арабскими цифрами и субциферблатом малых секунд на 6:00. Модель 1908 — возвращение Rolex к своим истокам: выпущена в 2023 году как дань уважения самым первым часам марки. Золотой флютированный безель, золотой браслет Jubilee и чистейший белый циферблат — элегантность вне времени.&lt;/p&gt; &lt;p&gt;❗️ НАМ ДОВЕРЯЮТ! ТОЛЬКО У НАС: Гарантия 1 год и 14 дней на проверку!&lt;/p&gt; &lt;p&gt;🔖 РАСПРОДАЖА до конца недели: напишите слово «Скидка» — вышлем промокод 5% на любые часы из профиля!&lt;/p&gt; &lt;p&gt;❗ Обязательно посмотрите видео до конца! Наше видео копируют и выдают за своё — будьте внимательны. Именно эти часы часто встречаются на Авито по завышенным ценам.&lt;/p&gt; &lt;p&gt;✅ Механизм: кварцевый&lt;/p&gt; &lt;p&gt;✅ Корпус и браслет Jubilee в цвете жёлтого золота&lt;/p&gt; &lt;p&gt;✅ Сапфировое стекло — устойчивое к царапинам&lt;/p&gt; &lt;p&gt;✅ Белый циферблат с арабскими цифрами и золотыми индексами&lt;/p&gt; &lt;p&gt;✅ Флютированный безель&lt;/p&gt; &lt;p&gt;✅ Субциферблат малых секунд на 6:00&lt;/p&gt; &lt;p&gt;✅ Корпус 39 мм&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;📷 Все фото и видео — реальные часы, которые вы получите. Без подмен.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ Каждая пара проходит полную проверку перед отправкой:&lt;/p&gt; &lt;p&gt;— внешний осмотр со всех сторон&lt;/p&gt; &lt;p&gt;— проверка механизма и точности хода&lt;/p&gt; &lt;p&gt;— работа всего функционала&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;❗️ Большинство продавцов отправляют без проверки — именно поэтому часы приезжают с браком. Мы проверяем всё заранее.&lt;/p&gt; &lt;p&gt;🚀 Быстрая отправка — в течение 24 часов после оформления заказа.&lt;/p&gt; &lt;p&gt;💳 Оплата через Авито — безопасная сделка. Не понравится при получении — можно отказаться.&lt;/p&gt; &lt;p&gt;🎁 Фирменный комплект (коробка, документы, пакет) — доступен отдельно.&lt;/p&gt; &lt;p&gt;🔥 Нашли дешевле? Напишите — сделаем лучшее предложение без потери качества.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;🚚 Авитодоставка по всей России — СДЭК, Яндекс, Почта России, Boxberry, DPD, 5Post, курьер.&lt;/p&gt; &lt;p&gt;&lt;br&gt;&lt;/p&gt; &lt;p&gt;⭐ В профиле большой выбор:  и другие. Кварцевые &lt;/p&gt;</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>Механические</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -19404,1370 +19404,1370 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_orange</t>
+          <t>i4_Hublot_Spirit_orange</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuU3o2j.jpg | https://iili.io/nuU3Epp.jpg | https://iili.io/nuU3Q8x.jpg | https://iili.io/nuUF2cJ.jpg | https://iili.io/nuUF5Al.jpg | https://iili.io/nuUFMSj.jpg</t>
+          <t>https://iili.io/nuU3o2j.jpg | https://iili.io/nuU3Epp.jpg | https://iili.io/nuU3Q8x.jpg | https://iili.io/nuUF2cJ.jpg | https://iili.io/nuUF5Al.jpg | https://iili.io/nuUFMSj.jpg</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оранжевый огонь — Hublot Spirit скелетон</t>
+          <t>Оранжевый огонь — Hublot Spirit скелетон</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — оранжевый, скелетон&lt;br&gt;&lt;br&gt;Бочкообразный корпус, открытый механизм и оранжевый каучук — часы, которые видно раньше, чем их владельца. Берут их не под костюм, а под футболку и кроссовки: там они работают как яркая деталь, ради которой к вам и подойдут с вопросом.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, оранжевый, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, три счётчика&lt;br&gt;▫️ Ремешок: каучук, оранжевый&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit of big bang, часы скелетон, наручные часы хронограф</t>
+          <t>⌚ Hublot Spirit of Big Bang — оранжевый, скелетон&lt;br&gt;&lt;br&gt;Бочкообразный корпус, открытый механизм и оранжевый каучук — часы, которые видно раньше, чем их владельца. Берут их не под костюм, а под футболку и кроссовки: там они работают как яркая деталь, ради которой к вам и подойдут с вопросом.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, оранжевый, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, три счётчика&lt;br&gt;▫️ Ремешок: каучук, оранжевый&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit of big bang, часы скелетон, наручные часы хронограф</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">15900</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оранжевый</t>
+          <t>Оранжевый</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+          <t>Hublot Spirit of Big Bang</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/CAOCBL7EisuAMg</t>
+          <t>https://disk.yandex.ru/i/CAOCBL7EisuAMg</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_yellow</t>
+          <t>i4_Hublot_Spirit_yellow</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUfYG9.jpg | https://iili.io/nuUf0Yb.jpg | https://iili.io/nuUfO3g.jpg | https://iili.io/nuUfDu4.jpg | https://iili.io/nuUqfAx.jpg | https://iili.io/nuUqgHb.jpg | https://iili.io/nuUBfgn.jpg | https://iili.io/nuUB1zQ.jpg | https://iili.io/nuUBrrX.jpg | https://iili.io/nuUBtQ2.jpg</t>
+          <t>https://iili.io/nuUfYG9.jpg | https://iili.io/nuUf0Yb.jpg | https://iili.io/nuUfO3g.jpg | https://iili.io/nuUfDu4.jpg | https://iili.io/nuUqfAx.jpg | https://iili.io/nuUqgHb.jpg | https://iili.io/nuUBfgn.jpg | https://iili.io/nuUB1zQ.jpg | https://iili.io/nuUBrrX.jpg | https://iili.io/nuUBtQ2.jpg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жёлтый неон — Hublot Spirit скелетон каучук</t>
+          <t>Жёлтый неон — Hublot Spirit скелетон каучук</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — жёлтый, скелетон&lt;br&gt;&lt;br&gt;Кислотный жёлтый — самый заметный цвет в линейке. Такие часы не теряются на руке ни летом, ни под тёмным рукавом, а открытый механизм добавляет им дорогого вида вблизи, когда собеседник уже присмотрелся.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, жёлтый, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, три счётчика&lt;br&gt;▫️ Ремешок: каучук, жёлтый&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit жёлтый, яркие часы мужские, наручные часы скелетон</t>
+          <t>⌚ Hublot Spirit of Big Bang — жёлтый, скелетон&lt;br&gt;&lt;br&gt;Кислотный жёлтый — самый заметный цвет в линейке. Такие часы не теряются на руке ни летом, ни под тёмным рукавом, а открытый механизм добавляет им дорогого вида вблизи, когда собеседник уже присмотрелся.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, жёлтый, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, три счётчика&lt;br&gt;▫️ Ремешок: каучук, жёлтый&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit жёлтый, яркие часы мужские, наручные часы скелетон</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">15900</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жёлтый</t>
+          <t>Жёлтый</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+          <t>Hublot Spirit of Big Bang</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/FSVpEQSox6h55A</t>
+          <t>https://disk.yandex.ru/i/FSVpEQSox6h55A</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_lightblue</t>
+          <t>i4_Hublot_Spirit_lightblue</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUCEyG.jpg | https://iili.io/nuUCMuf.jpg | https://iili.io/nuUCWZl.jpg | https://iili.io/nuUCw67.jpg | https://iili.io/nuUCk8u.jpg | https://iili.io/nuUCvyb.jpg</t>
+          <t>https://iili.io/nuUCEyG.jpg | https://iili.io/nuUCMuf.jpg | https://iili.io/nuUCWZl.jpg | https://iili.io/nuUCw67.jpg | https://iili.io/nuUCk8u.jpg | https://iili.io/nuUCvyb.jpg</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Голубая бочка — Hublot Spirit скелетон</t>
+          <t>Голубая бочка — Hublot Spirit скелетон</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — голубой, скелетон&lt;br&gt;&lt;br&gt;Голубой мягче синего и заметно реже встречается. Хорошо ложится на загорелую руку и спокойно живёт с джинсой — вариант для тех, кто хочет цвет, но без крика.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, голубой, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, синие счётчики&lt;br&gt;▫️ Ремешок: каучук, голубой&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit голубой, часы скелетон каучук, наручные часы кварц</t>
+          <t>⌚ Hublot Spirit of Big Bang — голубой, скелетон&lt;br&gt;&lt;br&gt;Голубой мягче синего и заметно реже встречается. Хорошо ложится на загорелую руку и спокойно живёт с джинсой — вариант для тех, кто хочет цвет, но без крика.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, голубой, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, синие счётчики&lt;br&gt;▫️ Ремешок: каучук, голубой&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit голубой, часы скелетон каучук, наручные часы кварц</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">15900</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Голубой</t>
+          <t>Голубой</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+          <t>Hublot Spirit of Big Bang</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/hWjS6rA8T_HhnA</t>
+          <t>https://disk.yandex.ru/i/hWjS6rA8T_HhnA</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_blue</t>
+          <t>i4_Hublot_Spirit_blue</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUnxPS.jpg | https://iili.io/nuUnRHu.jpg | https://iili.io/nuUncoQ.jpg | https://iili.io/nuUnMUF.jpg | https://iili.io/nuUnjDv.jpg | https://iili.io/nuUnvfI.jpg</t>
+          <t>https://iili.io/nuUnxPS.jpg | https://iili.io/nuUnRHu.jpg | https://iili.io/nuUncoQ.jpg | https://iili.io/nuUnMUF.jpg | https://iili.io/nuUnjDv.jpg | https://iili.io/nuUnvfI.jpg</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы Hublot Spirit синий скелетон каучук</t>
+          <t>Часы Hublot Spirit синий скелетон каучук</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — синий, скелетон&lt;br&gt;&lt;br&gt;Насыщенный синий — самый универсальный из ярких: сочетается и с джинсами, и с тёмным пиджаком. Открытый механизм видно и через циферблат, и через заднюю крышку.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, синий, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, синие счётчики&lt;br&gt;▫️ Ремешок: каучук, синий&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit синий, часы скелетон, наручные часы хронограф</t>
+          <t>⌚ Hublot Spirit of Big Bang — синий, скелетон&lt;br&gt;&lt;br&gt;Насыщенный синий — самый универсальный из ярких: сочетается и с джинсами, и с тёмным пиджаком. Открытый механизм видно и через циферблат, и через заднюю крышку.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, синий, чёрные винты по рамке&lt;br&gt;▫️ Циферблат: скелетон, синие счётчики&lt;br&gt;▫️ Ремешок: каучук, синий&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot spirit синий, часы скелетон, наручные часы хронограф</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">15900</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Синий</t>
+          <t>Синий</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+          <t>Hublot Spirit of Big Bang</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/sI_xfD8PJRMvfA</t>
+          <t>https://disk.yandex.ru/i/sI_xfD8PJRMvfA</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_carbon_red</t>
+          <t>i4_Hublot_Spirit_carbon_red</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUoXr7.jpg | https://iili.io/nuUoOmb.jpg | https://iili.io/nuUo8LQ.jpg | https://iili.io/nuUoPYF.jpg | https://iili.io/nuUobBp.jpg | https://iili.io/nuUxHYX.jpg</t>
+          <t>https://iili.io/nuUoXr7.jpg | https://iili.io/nuUoOmb.jpg | https://iili.io/nuUo8LQ.jpg | https://iili.io/nuUoPYF.jpg | https://iili.io/nuUobBp.jpg | https://iili.io/nuUxHYX.jpg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Карбон и красный — Hublot Spirit скелетон</t>
+          <t>Карбон и красный — Hublot Spirit скелетон</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон чёрно-красный, скелетон&lt;br&gt;&lt;br&gt;Корпус под карбон с красными разводами — рисунок у каждого экземпляра свой, двух одинаковых не бывает. Красные счётчики на тёмном скелетоне дают тот самый гоночный вид, за который эту линейку и берут.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-красный&lt;br&gt;▫️ Циферблат: скелетон, красные счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон, часы скелетон красные, наручные часы хронограф</t>
+          <t>⌚ Hublot Spirit of Big Bang — карбон чёрно-красный, скелетон&lt;br&gt;&lt;br&gt;Корпус под карбон с красными разводами — рисунок у каждого экземпляра свой, двух одинаковых не бывает. Красные счётчики на тёмном скелетоне дают тот самый гоночный вид, за который эту линейку и берут.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-красный&lt;br&gt;▫️ Циферблат: скелетон, красные счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон, часы скелетон красные, наручные часы хронограф</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">16900</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Красный</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit Carbon</t>
+          <t>Hublot Spirit Carbon</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/MoS0UZgvxSuB-g</t>
+          <t>https://disk.yandex.ru/i/MoS0UZgvxSuB-g</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_carbon_yellow</t>
+          <t>i4_Hublot_Spirit_carbon_yellow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUxjGp.jpg | https://iili.io/nuUxw6N.jpg | https://iili.io/nuUxeat.jpg | https://iili.io/nuUxUwG.jpg | https://iili.io/nuUxsFS.jpg | https://iili.io/nuUxQS9.jpg</t>
+          <t>https://iili.io/nuUxjGp.jpg | https://iili.io/nuUxw6N.jpg | https://iili.io/nuUxeat.jpg | https://iili.io/nuUxUwG.jpg | https://iili.io/nuUxsFS.jpg | https://iili.io/nuUxQS9.jpg</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Карбон и жёлтый — Hublot Spirit скелетон</t>
+          <t>Карбон и жёлтый — Hublot Spirit скелетон</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон чёрно-жёлтый, скелетон&lt;br&gt;&lt;br&gt;Тёмный карбон с жёлтыми прожилками и жёлтые стрелки — сочетание, которое читается даже издалека, но не выглядит пластиковым. Лёгкий корпус почти не чувствуется на руке.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-жёлтый&lt;br&gt;▫️ Циферблат: скелетон, жёлтые стрелки и счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон жёлтый, часы скелетон, наручные часы кварц</t>
+          <t>⌚ Hublot Spirit of Big Bang — карбон чёрно-жёлтый, скелетон&lt;br&gt;&lt;br&gt;Тёмный карбон с жёлтыми прожилками и жёлтые стрелки — сочетание, которое читается даже издалека, но не выглядит пластиковым. Лёгкий корпус почти не чувствуется на руке.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-жёлтый&lt;br&gt;▫️ Циферблат: скелетон, жёлтые стрелки и счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон жёлтый, часы скелетон, наручные часы кварц</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">16900</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Жёлтый</t>
+          <t>Жёлтый</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit Carbon</t>
+          <t>Hublot Spirit Carbon</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/Mo1EUnjoEmJ7Qg</t>
+          <t>https://disk.yandex.ru/i/Mo1EUnjoEmJ7Qg</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_carbon_green</t>
+          <t>i4_Hublot_Spirit_carbon_green</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUzlV4.jpg | https://iili.io/nuUzWJ9.jpg | https://iili.io/nuUzjDb.jpg | https://iili.io/nuUzvfV.jpg | https://iili.io/nuUzr5F.jpg | https://iili.io/nuUzsWv.jpg</t>
+          <t>https://iili.io/nuUzlV4.jpg | https://iili.io/nuUzWJ9.jpg | https://iili.io/nuUzjDb.jpg | https://iili.io/nuUzvfV.jpg | https://iili.io/nuUzr5F.jpg | https://iili.io/nuUzsWv.jpg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Карбон и зелёный — Hublot Spirit скелетон</t>
+          <t>Карбон и зелёный — Hublot Spirit скелетон</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон чёрно-зелёный, скелетон&lt;br&gt;&lt;br&gt;Зелёный по карбону — самая редкая расцветка линейки. На свету рисунок корпуса переливается, в тени часы выглядят почти чёрными: две разные вещи в одной.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-зелёный&lt;br&gt;▫️ Циферблат: скелетон, зелёные метки&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон зелёный, часы скелетон, наручные часы хронограф</t>
+          <t>⌚ Hublot Spirit of Big Bang — карбон чёрно-зелёный, скелетон&lt;br&gt;&lt;br&gt;Зелёный по карбону — самая редкая расцветка линейки. На свету рисунок корпуса переливается, в тени часы выглядят почти чёрными: две разные вещи в одной.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон чёрно-зелёный&lt;br&gt;▫️ Циферблат: скелетон, зелёные метки&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон зелёный, часы скелетон, наручные часы хронограф</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">16900</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зелёный</t>
+          <t>Зелёный</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit Carbon</t>
+          <t>Hublot Spirit Carbon</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/eHpwgSru5lD_0Q</t>
+          <t>https://disk.yandex.ru/i/eHpwgSru5lD_0Q</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_carbon_grey</t>
+          <t>i4_Hublot_Spirit_carbon_grey</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUIckF.jpg | https://iili.io/nuUIXrN.jpg | https://iili.io/nuUINkX.jpg | https://iili.io/nuUIUB4.jpg | https://iili.io/nuUIr42.jpg | https://iili.io/nuUIspe.jpg</t>
+          <t>https://iili.io/nuUIckF.jpg | https://iili.io/nuUIXrN.jpg | https://iili.io/nuUINkX.jpg | https://iili.io/nuUIUB4.jpg | https://iili.io/nuUIr42.jpg | https://iili.io/nuUIspe.jpg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы Hublot Spirit карбон серый скелетон</t>
+          <t>Часы Hublot Spirit карбон серый скелетон</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — карбон серый, скелетон&lt;br&gt;&lt;br&gt;Серый карбон без цветных вставок — вариант для тех, кому нужен характер линейки, но не нужен цвет. Такие часы одинаково уместны и с толстовкой, и с пиджаком.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон серый&lt;br&gt;▫️ Циферблат: скелетон, светлые счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон, часы скелетон серые, наручные часы кварц</t>
+          <t>⌚ Hublot Spirit of Big Bang — карбон серый, скелетон&lt;br&gt;&lt;br&gt;Серый карбон без цветных вставок — вариант для тех, кому нужен характер линейки, но не нужен цвет. Такие часы одинаково уместны и с толстовкой, и с пиджаком.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, карбон серый&lt;br&gt;▫️ Циферблат: скелетон, светлые счётчики&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot карбон, часы скелетон серые, наручные часы кварц</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">16900</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Серый</t>
+          <t>Серый</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit Carbon</t>
+          <t>Hublot Spirit Carbon</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/9zl4C0yF2bSSOg</t>
+          <t>https://disk.yandex.ru/i/9zl4C0yF2bSSOg</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_Spirit_black_matte</t>
+          <t>i4_Hublot_Spirit_black_matte</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUTjMx.jpg | https://iili.io/nuUTOFV.jpg | https://iili.io/nuUTSAF.jpg | https://iili.io/nuUT6Mv.jpg | https://iili.io/nuUTQSI.jpg | https://iili.io/nuUTbNn.jpg</t>
+          <t>https://iili.io/nuUTjMx.jpg | https://iili.io/nuUTOFV.jpg | https://iili.io/nuUTSAF.jpg | https://iili.io/nuUT6Mv.jpg | https://iili.io/nuUTQSI.jpg | https://iili.io/nuUTbNn.jpg</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чёрный матовый — Hublot Spirit скелетон</t>
+          <t>Чёрный матовый — Hublot Spirit скелетон</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Spirit of Big Bang — чёрный матовый, скелетон&lt;br&gt;&lt;br&gt;Полностью чёрный корпус без блеска — самая спокойная версия линейки и самая ходовая. Скелетон читается только вблизи, поэтому часы одновременно и сдержанные, и с секретом.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, чёрный матовый&lt;br&gt;▫️ Циферблат: скелетон, светлые стрелки&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot чёрные, часы скелетон, наручные часы хронограф</t>
+          <t>⌚ Hublot Spirit of Big Bang — чёрный матовый, скелетон&lt;br&gt;&lt;br&gt;Полностью чёрный корпус без блеска — самая спокойная версия линейки и самая ходовая. Скелетон читается только вблизи, поэтому часы одновременно и сдержанные, и с секретом.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый хронограф&lt;br&gt;▫️ Корпус: бочка, чёрный матовый&lt;br&gt;▫️ Циферблат: скелетон, светлые стрелки&lt;br&gt;▫️ Ремешок: каучук, чёрный&lt;br&gt;▫️ Функции: хронограф, секундомер, водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot чёрные, часы скелетон, наручные часы хронограф</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">16400</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чёрный</t>
+          <t>Чёрный</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Spirit of Big Bang</t>
+          <t>Hublot Spirit of Big Bang</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые | Хронограф | Секундомер</t>
+          <t>Водонепроницаемые | Хронограф | Секундомер</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/CDgH6picQ-ZMaw</t>
+          <t>https://disk.yandex.ru/i/CDgH6picQ-ZMaw</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">i4_Hublot_BigBang_red_rubber</t>
+          <t>i4_Hublot_BigBang_red_rubber</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Package</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">79337583089</t>
+          <t>79337583089</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Москва, Тверская улица</t>
+          <t>Москва, Тверская улица</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://iili.io/nuUuizu.jpg | https://iili.io/nuUA9mF.jpg | https://iili.io/nuUAFqv.jpg | https://iili.io/nuUAnet.jpg | https://iili.io/nuUATLG.jpg | https://iili.io/nuUA5rl.jpg</t>
+          <t>https://iili.io/nuUuizu.jpg | https://iili.io/nuUA9mF.jpg | https://iili.io/nuUAFqv.jpg | https://iili.io/nuUAnet.jpg | https://iili.io/nuUATLG.jpg | https://iili.io/nuUA5rl.jpg</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">По телефону и в сообщениях</t>
+          <t>По телефону и в сообщениях</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Красный каучук — часы Hublot Big Bang</t>
+          <t>Красный каучук — часы Hublot Big Bang</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌚ Hublot Big Bang — красный каучук, чёрный безель&lt;br&gt;&lt;br&gt;Круглый корпус Big Bang с чёрным безелем и цифрами по кругу, открытая механика в центре и красный каучук — классика бренда в самой узнаваемой подаче. Красный ремешок при желании меняется на чёрный за минуту.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: круглый, чёрный безель с цифрами&lt;br&gt;▫️ Циферблат: скелетон, красная стрелка&lt;br&gt;▫️ Ремешок: каучук, красный&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot big bang, часы скелетон красные, наручные часы</t>
+          <t>⌚ Hublot Big Bang — красный каучук, чёрный безель&lt;br&gt;&lt;br&gt;Круглый корпус Big Bang с чёрным безелем и цифрами по кругу, открытая механика в центре и красный каучук — классика бренда в самой узнаваемой подаче. Красный ремешок при желании меняется на чёрный за минуту.&lt;br&gt;&lt;br&gt;▫️ Механизм: кварцевый&lt;br&gt;▫️ Корпус: круглый, чёрный безель с цифрами&lt;br&gt;▫️ Циферблат: скелетон, красная стрелка&lt;br&gt;▫️ Ремешок: каучук, красный&lt;br&gt;▫️ Функции: водозащита&lt;br&gt;&lt;br&gt;📦 Модели и цвета разбирают быстро — перед заказом напишите в чат, проверю наличие и пришлю актуальные фото.&lt;br&gt;&lt;br&gt;🔍 При получении можно вскрыть и проверить в пункте выдачи — забираете, только если всё понравилось.&lt;br&gt;&lt;br&gt;🛠 Гарантия на механизм 1 год. Если с часами что-то не так — решаем без споров.&lt;br&gt;&lt;br&gt;🔄 Не подошла модель? Напишите — подберём замену из каталога.&lt;br&gt;&lt;br&gt;🚚 Авито Доставка по всей России.&lt;br&gt;&lt;br&gt;В профиле ещё больше моделей — загляните. Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;часы hublot мужские, hublot big bang, часы скелетон красные, наручные часы</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы и украшения</t>
+          <t>Часы и украшения</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">17900</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Часы</t>
+          <t>Часы</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Товар приобретен на продажу</t>
+          <t>Товар приобретен на продажу</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Новое</t>
+          <t>Новое</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot</t>
+          <t>Hublot</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Красный</t>
+          <t>Красный</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Да</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hublot Big Bang Red</t>
+          <t>Hublot Big Bang Red</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные или карманные</t>
+          <t>Наручные или карманные</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наручные часы</t>
+          <t>Наручные часы</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мужские</t>
+          <t>Мужские</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кварцевые</t>
+          <t>Кварцевые</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Водонепроницаемые</t>
+          <t>Водонепроницаемые</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каучуковый</t>
+          <t>Каучуковый</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://disk.yandex.ru/i/cqq1WxdWQ2eGnQ</t>
+          <t>https://disk.yandex.ru/i/cqq1WxdWQ2eGnQ</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t xml:space="preserve">ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Электроника С Гарантией</t>
+          <t>Электроника С Гарантией</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t xml:space="preserve">golodnovewan@yandex.ru</t>
+          <t>golodnovewan@yandex.ru</t>
         </is>
       </c>
     </row>

--- a/ivan_feed.xlsx
+++ b/ivan_feed.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спр-Часы-Наручные или карманные" sheetId="5" state="hidden" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Противоугонные-Спутниковые сист" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спр-Противоугонные-Спутниковые " sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Фототехника-Бинокли и телескопы" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Спр-Фототехника-Бинокли и телес" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="Instructions" localSheetId="0">Инструкция!$1:$50</definedName>
@@ -1382,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="50" customHeight="1">
@@ -2623,6 +2625,374 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>n0925_YM_M28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>79337583089</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Москва, ул. Сущёвский Вал, 5с15</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Фонарь EDC аккумуляторный Yemao M28 880 лм белый</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>🔦 EDC фонарь Yemao M28 — плоский карманный фонарик 880 люмен с боковой COB-панелью, ультрафиолетом и дисплеем заряда. Корпус толщиной 12 мм, белый.&lt;br&gt;&lt;br&gt;📌 Перед заказом напишите в чат — проверю наличие и отправлю в тот же день.&lt;br&gt;&lt;br&gt;Обычный фонарик в кармане — это цилиндр, который давит в бедро. M28 плоский, как зажигалка: 12 мм толщины, клипса с двух сторон — носится на ремне, в кармане джинсов, на лямке рюкзака или на козырьке кепки вместо налобника. Спереди — сфокусированный луч 880 лм, сбоку — широкая COB-панель для работы в упор, красный свет и УФ. Сколько осталось заряда, видно на цифровом дисплее в процентах.&lt;br&gt;&lt;br&gt;Характеристики:&lt;br&gt;⚡ Яркость до 880 люмен, двойной диод XPL + фитиль&lt;br&gt;⚡ 13 режимов: 8 основного света + 5 бокового&lt;br&gt;⚡ Боковая COB-панель: белый, красный, ультрафиолет, красная вспышка&lt;br&gt;⚡ Цифровой дисплей заряда в %&lt;br&gt;⚡ Зарядка USB Type-C&lt;br&gt;⚡ Корпус из нержавеющей стали, порошковая покраска, противоскользящее покрытие&lt;br&gt;⚡ Толщина 12 мм, двусторонняя клипса&lt;br&gt;&lt;br&gt;📍 Где пригодится: каждый день в кармане, в машину на случай поломки, гараж и ремонт, прогулка с собакой, рыбалка, поход, проверка купюр ультрафиолетом.&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь Yemao M28, кабель Type-C, коробка.&lt;br&gt;&lt;br&gt;🎁 Подарок мужчине, автомобилисту, туристу — вещь, которой пользуются каждый день.&lt;br&gt;&lt;br&gt;🛡 Гарантия 1 год — если что-то не так, меняем.&lt;br&gt;🚚 Авито Доставка по всей России: СДЭК, Яндекс, Почта, Boxberry, 5Post. Отправка в день заказа.&lt;br&gt;💸 −10% при заказе от 2 любых товаров — скидка применяется автоматически.&lt;br&gt;❤️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Часто ищут как: фонарик edc, плоский фонарь на клипсе, фонарь с ультрафиолетом, карманный фонарик аккумуляторный, фонарь Yemao.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://iili.io/nRTPyS1.jpg | https://iili.io/nRTialS.jpg | https://iili.io/nRTiw0B.jpg | https://iili.io/nRTi8ba.jpg | https://iili.io/nRTiLJt.jpg | https://iili.io/nRTibzG.jpg | https://iili.io/nRTsJgS.jpg | https://iili.io/nRTsu71.jpg | https://iili.io/nRTsVkX.jpg | https://iili.io/nRTsUv9.jpg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Спорт и отдых</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Туризм и отдых на природе</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Фонари и лампы</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/i/Rq35-eJvO-dyPg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>n0925_YM_M52</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>79337583089</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Москва, проспект Вернадского</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Фонарь мини аккумуляторный Yemao M52 1500 лм</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>🔦 Мини фонарь Yemao M52 — маленький аккумуляторный фонарик на 1500 люмен, помещается в карман джинсов. Магнит, клипса, красно-синий сигнал.&lt;br&gt;&lt;br&gt;📌 Перед заказом напишите в чат — проверю наличие и отправлю в тот же день.&lt;br&gt;&lt;br&gt;Мощный фонарь чаще всего лежит дома — носить его неудобно. M52 меньше ладони и весит как связка ключей, поэтому он всегда с собой. При этом выдаёт 1500 люмен и бьёт на 80 метров — как фонарь втрое крупнее. Магнит в хвосте держит его на капоте или батарее, пока руки заняты, а красно-синяя вспышка обозначит машину на трассе.&lt;br&gt;&lt;br&gt;Характеристики:&lt;br&gt;⚡ Яркость до 1500 люмен, луч до 80 м&lt;br&gt;⚡ 6 режимов: максимум, средний, эконом, стробоскоп, аварийный, красно-синяя вспышка&lt;br&gt;⚡ Аккумулятор 14500 в комплекте — до 10 часов&lt;br&gt;⚡ Зарядка USB Type-C&lt;br&gt;⚡ Алюминиевый корпус, влагозащита IPX4&lt;br&gt;⚡ Магнит и клипса — крепится на карман и кепку&lt;br&gt;&lt;br&gt;📍 Где пригодится: в кармане каждый день, в бардачок, рыбалка, охота, поход, гараж, дом.&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь, аккумулятор 14500, кабель Type-C, инструкция, коробка.&lt;br&gt;&lt;br&gt;🎁 Недорогой подарок мужчине, который реально пригодится.&lt;br&gt;&lt;br&gt;🛡 Гарантия 1 год — если что-то не так, меняем.&lt;br&gt;🚚 Авито Доставка по всей России: СДЭК, Яндекс, Почта, Boxberry, 5Post. Отправка в день заказа.&lt;br&gt;💸 −10% при заказе от 2 любых товаров — скидка применяется автоматически.&lt;br&gt;❤️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Часто ищут как: маленький фонарик мощный, мини фонарь аккумуляторный, карманный фонарь с магнитом, фонарь Yemao, edc фонарик.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://iili.io/nRTLZoG.jpg | https://iili.io/nRTLpl2.jpg | https://iili.io/nRTQBKQ.jpg | https://iili.io/nRTQAxa.jpg | https://iili.io/nRTQalp.jpg | https://iili.io/nRTQcUN.jpg | https://iili.io/nRTQjf4.jpg | https://iili.io/nRTQigV.jpg | https://iili.io/nRTZqIn.jpg | https://iili.io/nRTZlBj.jpg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Спорт и отдых</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Туризм и отдых на природе</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Фонари и лампы</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/i/AmvGzXRRVzi92Q</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>n0925_YM_M31</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>79337583089</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Москва, Селезнёвская улица</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Фонарь EDC Yemao M31 с магнитом 16 режимов RGB</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>🔦 EDC фонарь Yemao M31 — многофункциональный карманный фонарик: 680 люмен, RGB-подсветка, магнит, крюк, велокрепление и линейка.&lt;br&gt;&lt;br&gt;📌 Перед заказом напишите в чат — проверю наличие и отправлю в тот же день.&lt;br&gt;&lt;br&gt;M31 — это несколько инструментов в одном корпусе весом 75 грамм. Основной диод бьёт сфокусированным лучом на 95 метров, боковая панель светит красным для ночного зрения, синим — как аварийный сигнал, зелёным — на охоте, тёплым белым — в палатке. Три отдельные кнопки — нужный режим сразу, без перелистывания. Магнит, складной крюк, зажим на кепку и велокрепление в комплекте. Цвет корпуса: оранжевый, зелёный, серый или чёрный — если важен конкретный, напишите.&lt;br&gt;&lt;br&gt;Характеристики:&lt;br&gt;⚡ Диод P50 — до 680 люмен, луч до 95 м&lt;br&gt;⚡ 16 режимов, 3 отдельные кнопки&lt;br&gt;⚡ RGB-панель: красный, синий, зелёный, тёплый белый + стробоскоп&lt;br&gt;⚡ Магнит в хвосте, складной крюк, зажим-трансформер&lt;br&gt;⚡ Встроенная линейка 10 см&lt;br&gt;⚡ Вес 75 г, зарядка USB Type-C&lt;br&gt;&lt;br&gt;📍 Где пригодится: каждый день в кармане, велосипед, кемпинг и палатка, охота, рыбалка, гараж, авто.&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарь Yemao M31, велокрепление, кабель Type-C, коробка.&lt;br&gt;&lt;br&gt;🎁 Подарок туристу, велосипедисту, автомобилисту — «тому, у кого всё есть».&lt;br&gt;&lt;br&gt;🛡 Гарантия 1 год — если что-то не так, меняем.&lt;br&gt;🚚 Авито Доставка по всей России: СДЭК, Яндекс, Почта, Boxberry, 5Post. Отправка в день заказа.&lt;br&gt;💸 −10% при заказе от 2 любых товаров — скидка применяется автоматически.&lt;br&gt;❤️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Часто ищут как: фонарь с магнитом и крючком, edc фонарь многофункциональный, велофонарь аккумуляторный, фонарик с красным светом, фонарь Yemao M31.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://iili.io/nRTtxZg.jpg | https://iili.io/nRTtRFR.jpg | https://iili.io/nRTt5ap.jpg | https://iili.io/nRTta9I.jpg | https://iili.io/nRTtlwX.jpg | https://iili.io/nRTtEns.jpg | https://iili.io/nRTtWF4.jpg | https://iili.io/nRTtNA7.jpg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Спорт и отдых</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Туризм и отдых на природе</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Фонари и лампы</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/i/1E3OqZzH2Q-HLQ</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>n0925_YM_M02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>79337583089</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Москва, Окская улица</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Фонарик-брелок на ключи Yemao M02X 280 лм УФ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>🔑 Фонарик-брелок на ключи Yemao M02X — маленький аккумуляторный фонарь 280 люмен с ультрафиолетом. Висит на связке ключей и всегда под рукой.&lt;br&gt;&lt;br&gt;📌 Перед заказом напишите в чат — проверю наличие и отправлю в тот же день.&lt;br&gt;&lt;br&gt;Лучший фонарь — тот, что с собой. Этот живёт на ключах и достаётся за секунду: тёмный подъезд, замочная скважина, ключи под сиденьем, щиток в гараже. Двойное нажатие — турбо 280 люмен на 30 метров, для брелока это очень много. УФ-режим проверит купюры и документы. Батареек нет — заряжается от Type-C за пару часов.&lt;br&gt;&lt;br&gt;Характеристики:&lt;br&gt;⚡ До 280 люмен, дальность до 30 м&lt;br&gt;⚡ Ультрафиолетовый режим&lt;br&gt;⚡ Режимы: яркий, эконом, стробоскоп, SOS&lt;br&gt;⚡ До 22 часов в экономе&lt;br&gt;⚡ Зарядка USB Type-C ~2 часа&lt;br&gt;⚡ Авиационный алюминий, влагозащита IP44&lt;br&gt;&lt;br&gt;📍 Где пригодится: на ключи, молнию рюкзака, шлёвку джинсов; в машину, на рыбалку, в поход.&lt;br&gt;&lt;br&gt;📦 В комплекте: фонарик Yemao M02X, кабель Type-C, упаковка.&lt;br&gt;&lt;br&gt;🎁 Недорогой полезный подарок — берут по 2–3 штуки, себе и в подарок.&lt;br&gt;&lt;br&gt;🛡 Гарантия 1 год — если что-то не так, меняем.&lt;br&gt;🚚 Авито Доставка по всей России: СДЭК, Яндекс, Почта, Boxberry, 5Post. Отправка в день заказа.&lt;br&gt;💸 −10% при заказе от 2 любых товаров — скидка применяется автоматически.&lt;br&gt;❤️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Часто ищут как: фонарик на ключи, брелок фонарик аккумуляторный, маленький фонарик с ультрафиолетом, мини фонарь брелок, фонарь Yemao.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://iili.io/nRTDmXe.jpg | https://iili.io/nRTbqI1.jpg | https://iili.io/nRTb7It.jpg | https://iili.io/nRTbeEb.jpg | https://iili.io/nRTmett.jpg | https://iili.io/nRTpNgj.jpg | https://iili.io/nRTyKp2.jpg | https://iili.io/nRu90tS.jpg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Спорт и отдых</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Туризм и отдых на природе</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Фонари и лампы</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/i/5HEvzmnfMT2kTA</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>golodnovewan@yandex.ru</t>
         </is>
@@ -76184,4 +76554,546 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Электроника - Фототехника - Бинокли и телескопы</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Уникальный идентификатор объявления</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Способ размещения</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Номер объявления на Авито</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Контактное лицо</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Номер телефона</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Адрес</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Название объявления</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Описание объявления</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Ссылки на фото</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Названия фото</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Способ связи</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Вид товара</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Вид объявления</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>URL видеофайла</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Способ доставки</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>WholesaleTypePredict2Param</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Название компании</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Почта</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>AvitoDateEnd</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>AvitoStatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Обязательный</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Необязательный</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Подробнее о параметре</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Целое число</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Одно значение из выпадающего списка в ячейке</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>n0925_LY_3060</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>79337583089</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Москва, Калужско-Рижская линия, метро ВДНХ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Бинокль мини карманный х15 для рыбалки и туризма</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>🔭 Мини бинокль карманный — компактный бинокль с увеличением х15 размером с ладонь. Для рыбалки, туризма, стадиона и театра.&lt;br&gt;&lt;br&gt;📌 Перед заказом напишите в чат — проверю наличие и отправлю в тот же день.&lt;br&gt;&lt;br&gt;Большой бинокль остаётся дома — он тяжёлый. Этот помещается в карман куртки или бардачок и весит как смартфон, поэтому оказывается с собой именно тогда, когда нужен: номер машины, птица на дереве, поплавок на том берегу, сцена с дальнего ряда. Просветлённые линзы дают яркую картинку в сумерках и не запотевают.&lt;br&gt;&lt;br&gt;Характеристики:&lt;br&gt;⚡ Увеличение х15, детали видно до 1 км&lt;br&gt;⚡ Многослойное просветление линз&lt;br&gt;⚡ Защита от запотевания&lt;br&gt;⚡ Корпус ABS с резиновым покрытием&lt;br&gt;⚡ Размер с ладонь&lt;br&gt;&lt;br&gt;📍 Где пригодится: рыбалка, охота, походы, путешествия, стадион, театр, наблюдение за птицами; подросткам вместо очередной игрушки.&lt;br&gt;&lt;br&gt;📦 В комплекте: бинокль, чехол, шнурок на руку/шею, салфетка для линз, инструкция.&lt;br&gt;&lt;br&gt;🎁 Подарок рыбаку, туристу или ребёнку-исследователю.&lt;br&gt;&lt;br&gt;🛡 Гарантия 1 год — если что-то не так, меняем.&lt;br&gt;🚚 Авито Доставка по всей России: СДЭК, Яндекс, Почта, Boxberry, 5Post. Отправка в день заказа.&lt;br&gt;💸 −10% при заказе от 2 любых товаров — скидка применяется автоматически.&lt;br&gt;❤️ Добавьте в избранное, чтобы не потерять.&lt;br&gt;&lt;br&gt;Часто ищут как: бинокль компактный, маленький бинокль, бинокль театральный, бинокль для рыбалки, карманный бинокль недорого.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://iili.io/nRuJk6F.jpg | https://iili.io/nRud2M7.jpg | https://iili.io/nRudxtV.jpg | https://iili.io/nRudcAv.jpg | https://iili.io/nRud4Uu.jpg | https://iili.io/nRu2WXV.jpg | https://iili.io/nRu2ZkG.jpg | https://iili.io/nRu3BhQ.jpg | https://iili.io/nRu3RyJ.jpg | https://iili.io/nRu3Man.jpg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Фототехника</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Бинокли и телескопы</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://disk.yandex.ru/i/MXlQHhbNCash8Q</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ПВЗ | Курьер | Постамат | Самовывоз с онлайн-оплатой</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Электроника С Гарантией</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>golodnovewan@yandex.ru</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Способ размещения</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Способ связи</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Вид товара</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Вид объявления</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Состояние</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>По телефону и в сообщениях</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Фототехника</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Компактные фотоаппараты</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Продаю своё</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PackageBBL</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>По телефону</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Зеркальные фотоаппараты</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Б/у</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BBL</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>В сообщениях</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Плёночные фотоаппараты</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Бинокли и телескопы</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Объективы</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Оборудование и аксессуары</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>